--- a/Cruce_Obligaciones_Financieras_62_Jul2026.xlsx
+++ b/Cruce_Obligaciones_Financieras_62_Jul2026.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6155" uniqueCount="1530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6193" uniqueCount="1557">
   <si>
     <t xml:space="preserve">GUAICARAMO S.A.S. – Auditoría de Obligaciones Financieras (cuenta 21 / papel 62) – corte 31-jul-2026</t>
   </si>
@@ -3516,6 +3516,9 @@
     <t xml:space="preserve">Pago 28-jul-26 de $206.288.000 vs intereses facturados $206.287.213,20: excedente $786,80 se aplica a capital.</t>
   </si>
   <si>
+    <t xml:space="preserve">p.14 + LEASING_1275-3_DAVIVIENDA.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Davivienda Leasing</t>
   </si>
   <si>
@@ -3570,12 +3573,18 @@
     <t xml:space="preserve">Saldo tras pago 20-abr-26; canon 20-jul-26 capital $21.542.838,16 / costo financiero $14.121.779,84. DTF.</t>
   </si>
   <si>
+    <t xml:space="preserve">p.22 + LEASING_9441-2_DAVIVIENDA.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">000030001019441-2</t>
   </si>
   <si>
     <t xml:space="preserve">Canon 033 (13-jul-26): capital $12.327.298, intereses $5.062.372, seguro $1.263.646. Último pago 11-jun-26 canon 032 $1.029.562 (sólo intereses). Sin saldo de capital.</t>
   </si>
   <si>
+    <t xml:space="preserve">p.24 + LEASING_9448-3_DAVIVIENDA.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">000030001019448-3</t>
   </si>
   <si>
@@ -3723,6 +3732,75 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">D. Documentos Davivienda Leasing recibidos por separado (LEASING_1275-3 / 9441-2 / 9448-3_DAVIVIENDA.pdf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canon / fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital canon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intereses canon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa EA cobrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Último pago (fecha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Último pago (valor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Informa saldo capital?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coincide intereses con papel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coincide capital con papel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coincide tasa con papel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEASING_1275-3_DAVIVIENDA.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">006 / 2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mismo documento que el PDF consolidado. Sólo factura del canon: el saldo de capital sigue sin certificar (PEND-1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEASING_9441-2_DAVIVIENDA.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">033 / 2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mismo documento que el PDF consolidado. Sólo factura del canon: el saldo de capital sigue sin certificar (PEND-1). Reconfirma canon 032 pagado sólo con intereses $1.029.562 (PEND-7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEASING_9448-3_DAVIVIENDA.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">031 / 2026-07-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cruce detalle 62 vs mayor (cuentas 2105 y 2120) – Integridad y exactitud</t>
   </si>
   <si>
@@ -4548,24 +4626,27 @@
     <t xml:space="preserve">2, 3, 13</t>
   </si>
   <si>
+    <t xml:space="preserve">Parcial – recibido sin saldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usa el saldo del detalle 62; saldo implícito estimado en Recalculo_Intereses Parte 3. Recibidos LEASING_1275-3/9441-2/9448-3_DAVIVIENDA.pdf: son facturas de canon sin saldo de capital (Certificados sección D).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEND-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificados de saldo de los leasings Bancolombia 362095, 336817, 331330 y contrato + tabla de amortización del nuevo leasing 386735.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL-L362095 / L336817 / L331330 / L386735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 2, 3, 13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pendiente</t>
   </si>
   <si>
-    <t xml:space="preserve">Se usa el saldo del detalle 62; saldo implícito estimado en Recalculo_Intereses Parte 3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEND-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificados de saldo de los leasings Bancolombia 362095, 336817, 331330 y contrato + tabla de amortización del nuevo leasing 386735.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCL-L362095 / L336817 / L331330 / L386735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, 2, 3, 13</t>
-  </si>
-  <si>
     <t xml:space="preserve">Residual de leasing sin explicar queda abierto; 386735 se toma del mayor (NB-1014).</t>
   </si>
   <si>
@@ -4629,10 +4710,13 @@
     <t xml:space="preserve">11</t>
   </si>
   <si>
-    <t xml:space="preserve">Davivienda Leasing / cliente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin ajuste hasta verificar.</t>
+    <t xml:space="preserve">Cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial – banco reconfirma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin ajuste hasta verificar. LEASING_9441-2_DAVIVIENDA.pdf reconfirma el lado del banco; falta la explicación del cliente del registro CL-416.</t>
   </si>
   <si>
     <t xml:space="preserve">PEND-8</t>
@@ -4647,9 +4731,6 @@
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">Cliente</t>
-  </si>
-  <si>
     <t xml:space="preserve">AJE-2 calculado con el CP del detalle 62 corregido; sujeto a validación.</t>
   </si>
   <si>
@@ -4701,7 +4782,7 @@
     <t xml:space="preserve">Pendientes abiertos</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrucción: al recibir un soporte, cambiar el Estado a 'Recibido', actualizar los datos de entrada (azul) en la hoja correspondiente y recalcular.</t>
+    <t xml:space="preserve">Instrucción: al recibir un soporte suficiente, cambiar el Estado a 'Recibido' (se descuenta del contador), actualizar los datos de entrada (azul) en la hoja correspondiente y recalcular.</t>
   </si>
 </sst>
 </file>
@@ -4719,7 +4800,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.0&quot; pb&quot;;\(#,##0.0&quot; pb)&quot;;\-"/>
     <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd;;&quot;sin reversión&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4813,6 +4894,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -5043,6 +5132,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5051,11 +5144,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5085,10 +5178,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -6005,12 +6094,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1347</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1348</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6018,22 +6107,22 @@
         <v>987</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1349</v>
+        <v>1375</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1350</v>
+        <v>1376</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1351</v>
+        <v>1377</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>1352</v>
+        <v>1378</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>1353</v>
+        <v>1379</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1354</v>
+        <v>1380</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>993</v>
@@ -6067,13 +6156,13 @@
         <f aca="false">-Balance_21!$F$18</f>
         <v>20362333333</v>
       </c>
-      <c r="H5" s="37" t="s">
-        <v>1355</v>
+      <c r="H5" s="35" t="s">
+        <v>1381</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1356</v>
+        <v>1382</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$M$14:$M$35,Detalle_62!$D$14:$D$35,"Leasing")</f>
@@ -6099,13 +6188,13 @@
         <f aca="false">-Balance_21!$F$24</f>
         <v>6745268240.93</v>
       </c>
-      <c r="H6" s="37" t="s">
-        <v>1357</v>
+      <c r="H6" s="35" t="s">
+        <v>1383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B7" s="20" t="n">
         <f aca="false">B5+B6</f>
@@ -6134,7 +6223,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>1358</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6142,7 +6231,7 @@
         <v>987</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1359</v>
+        <v>1385</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -6155,7 +6244,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>1360</v>
+        <v>1386</v>
       </c>
       <c r="B11" s="38" t="n">
         <f aca="false">D5-F5</f>
@@ -6164,19 +6253,19 @@
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>1361</v>
+        <v>1387</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">D6-(F6-SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,"BCL-L386735",Mayor_Mov!$B$5:$B$445,"21202040"))</f>
         <v>2101451761.47034</v>
       </c>
-      <c r="H12" s="37" t="s">
-        <v>1362</v>
+      <c r="H12" s="35" t="s">
+        <v>1388</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1363</v>
+        <v>1389</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">-Balance_21!$F$19</f>
@@ -6185,7 +6274,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>1364</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6193,21 +6282,21 @@
         <v>1021</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1365</v>
+        <v>1391</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1366</v>
+        <v>1392</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1367</v>
+        <v>1393</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>1368</v>
+        <v>1394</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>1369</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6230,8 +6319,8 @@
         <f aca="false">C17+D17-B17</f>
         <v>252940565.791742</v>
       </c>
-      <c r="H17" s="37" t="s">
-        <v>1370</v>
+      <c r="H17" s="35" t="s">
+        <v>1396</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6254,8 +6343,8 @@
         <f aca="false">C18+D18-B18</f>
         <v>0</v>
       </c>
-      <c r="H18" s="37" t="s">
-        <v>1371</v>
+      <c r="H18" s="35" t="s">
+        <v>1397</v>
       </c>
     </row>
   </sheetData>
@@ -6289,12 +6378,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1372</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1373</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6302,19 +6391,19 @@
         <v>1096</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1374</v>
+        <v>1400</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1375</v>
+        <v>1401</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1376</v>
+        <v>1402</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>1377</v>
+        <v>1403</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>1378</v>
+        <v>1404</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>13</v>
@@ -6325,23 +6414,23 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1379</v>
+        <v>1405</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1380</v>
+        <v>1406</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">Cruce_Detalle_Mayor!F14</f>
         <v>675837500</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1381</v>
+        <v>1407</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1382</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>1383</v>
+        <v>1408</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6349,23 +6438,23 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1384</v>
+        <v>1410</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1385</v>
+        <v>1411</v>
       </c>
       <c r="D6" s="11" t="n">
         <f aca="false">Cruce_Detalle_Mayor!F7</f>
         <v>1018266176.70086</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1386</v>
+        <v>1412</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1387</v>
-      </c>
-      <c r="G6" s="45" t="s">
-        <v>1388</v>
+        <v>1413</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>1414</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6373,23 +6462,23 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1389</v>
+        <v>1415</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1390</v>
+        <v>1416</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">Cruce_Detalle_Mayor!F16</f>
         <v>170820422.336308</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1391</v>
+        <v>1417</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1392</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>1388</v>
+        <v>1418</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>1414</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6397,23 +6486,23 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1389</v>
+        <v>1415</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1393</v>
+        <v>1419</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">-Certificados!$L$23</f>
         <v>171608254.364557</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>1394</v>
+        <v>1420</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1395</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>1383</v>
+        <v>1421</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6421,23 +6510,23 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1396</v>
+        <v>1422</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1397</v>
+        <v>1423</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K47</f>
         <v>188283769.079588</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1398</v>
+        <v>1424</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G9" s="45" t="s">
-        <v>1400</v>
+        <v>1425</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>1426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6445,23 +6534,23 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1389</v>
+        <v>1415</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1401</v>
+        <v>1427</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K7+Recalculo_Intereses!K8</f>
         <v>-51336719.6488978</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1402</v>
+        <v>1428</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>1404</v>
+        <v>1429</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>1430</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6469,22 +6558,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1405</v>
+        <v>1431</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1406</v>
+        <v>1432</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>1408</v>
+        <v>1434</v>
       </c>
       <c r="F11" s="10" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G11" s="45" t="s">
         <v>1409</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6492,23 +6581,23 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1410</v>
+        <v>1436</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">Clasif_CP_LP!B11+Clasif_CP_LP!B12</f>
         <v>2817285095.14034</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1412</v>
+        <v>1438</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>1413</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>1414</v>
+        <v>1439</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>1440</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6516,23 +6605,23 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1410</v>
+        <v>1436</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1415</v>
+        <v>1441</v>
       </c>
       <c r="D13" s="11" t="n">
         <f aca="false">Clasif_CP_LP!B13</f>
         <v>31135731.73</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1416</v>
+        <v>1442</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>1417</v>
-      </c>
-      <c r="G13" s="44" t="s">
-        <v>1383</v>
+        <v>1443</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6540,23 +6629,23 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1389</v>
+        <v>1415</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1418</v>
+        <v>1444</v>
       </c>
       <c r="D14" s="12" t="n">
         <f aca="false">127.57+269.47+627.79+617.95+786.8</f>
         <v>2429.58</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>1419</v>
+        <v>1445</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>1383</v>
+        <v>1446</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6564,22 +6653,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1421</v>
+        <v>1447</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1422</v>
+        <v>1448</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>11973677</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1394</v>
+        <v>1420</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>1424</v>
+        <v>1449</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>1450</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6587,23 +6676,23 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1425</v>
+        <v>1451</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1426</v>
+        <v>1452</v>
       </c>
       <c r="D16" s="12" t="n">
         <f aca="false">4068134+31360500+8261283</f>
         <v>43689917</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1427</v>
+        <v>1453</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>1383</v>
+        <v>1454</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6611,23 +6700,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1429</v>
+        <v>1455</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1430</v>
+        <v>1456</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">Certificados!K34</f>
         <v>6758520534.1583</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1431</v>
+        <v>1457</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>1432</v>
-      </c>
-      <c r="G17" s="45" t="s">
-        <v>1433</v>
+        <v>1458</v>
+      </c>
+      <c r="G17" s="46" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6635,22 +6724,22 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1405</v>
+        <v>1431</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1435</v>
+        <v>1461</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1436</v>
-      </c>
-      <c r="G18" s="44" t="s">
-        <v>1383</v>
+        <v>1462</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6658,22 +6747,22 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1437</v>
+        <v>1463</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1438</v>
+        <v>1464</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1439</v>
+        <v>1465</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G19" s="45" t="s">
-        <v>1441</v>
+        <v>1466</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>1467</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6681,22 +6770,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1425</v>
+        <v>1451</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1442</v>
+        <v>1468</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1443</v>
+        <v>1469</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>1383</v>
+        <v>1470</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6704,28 +6793,28 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1379</v>
+        <v>1405</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1445</v>
+        <v>1471</v>
       </c>
       <c r="D21" s="11" t="n">
         <f aca="false">Cruce_Mov_Balance!H12</f>
         <v>-2.60770320892334E-008</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1447</v>
-      </c>
-      <c r="G21" s="44" t="s">
-        <v>1383</v>
+        <v>1473</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>1409</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1448</v>
+        <v>1474</v>
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
@@ -6735,7 +6824,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>1449</v>
+        <v>1475</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>68</v>
@@ -6750,18 +6839,18 @@
         <v>72</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>1218</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>964</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1451</v>
+        <v>1477</v>
       </c>
       <c r="D25" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K48</f>
@@ -6769,18 +6858,18 @@
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="10" t="s">
-        <v>1452</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>681</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1453</v>
+        <v>1479</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="11" t="n">
@@ -6791,13 +6880,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>966</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1454</v>
+        <v>1480</v>
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K49</f>
@@ -6805,18 +6894,18 @@
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="10" t="s">
-        <v>1455</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>802</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1456</v>
+        <v>1482</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="11" t="n">
@@ -6827,13 +6916,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1458</v>
+        <v>1484</v>
       </c>
       <c r="D29" s="11" t="n">
         <f aca="false">Clasif_CP_LP!B11</f>
@@ -6841,18 +6930,18 @@
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="10" t="s">
-        <v>1459</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>83</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1460</v>
+        <v>1486</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="11" t="n">
@@ -6863,13 +6952,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>567</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1461</v>
+        <v>1487</v>
       </c>
       <c r="D31" s="11" t="n">
         <f aca="false">Clasif_CP_LP!B12</f>
@@ -6880,13 +6969,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>548</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1462</v>
+        <v>1488</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="11" t="n">
@@ -6897,7 +6986,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="19" t="s">
-        <v>1463</v>
+        <v>1489</v>
       </c>
       <c r="D33" s="20" t="n">
         <f aca="false">SUM(D25:D32)</f>
@@ -6910,7 +6999,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="2" t="s">
-        <v>1464</v>
+        <v>1490</v>
       </c>
     </row>
   </sheetData>
@@ -6945,100 +7034,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1465</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1466</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>1467</v>
+        <v>1493</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1468</v>
+        <v>1494</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1469</v>
+        <v>1495</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1470</v>
+        <v>1496</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>1471</v>
+        <v>1497</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>1472</v>
+        <v>1498</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>1474</v>
+        <v>1500</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1475</v>
+        <v>1501</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1476</v>
+        <v>1502</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K58</f>
         <v>2605824073.83539</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1477</v>
+        <v>1503</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>1478</v>
+        <v>1504</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>1479</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>1480</v>
+        <v>1506</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1481</v>
+        <v>1507</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1482</v>
+        <v>1508</v>
       </c>
       <c r="D6" s="11" t="n">
         <f aca="false">Cruce_Detalle_Mayor!F16</f>
         <v>170820422.336308</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1483</v>
+        <v>1509</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>1119</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1484</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>1485</v>
+        <v>1512</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1486</v>
+        <v>1513</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>91</v>
@@ -7048,24 +7137,24 @@
         <v>50972239.5760856</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1487</v>
+        <v>1514</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1488</v>
+        <v>1515</v>
       </c>
       <c r="G7" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1489</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>1490</v>
+        <v>1517</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1491</v>
+        <v>1518</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>140</v>
@@ -7075,24 +7164,24 @@
         <v>287500000</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1492</v>
+        <v>1519</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1493</v>
+        <v>1520</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1494</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>1495</v>
+        <v>1522</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1496</v>
+        <v>1523</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>102</v>
@@ -7102,27 +7191,27 @@
         <v>30518760.5171553</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1487</v>
+        <v>1514</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>1115</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1497</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>1498</v>
+        <v>1525</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1499</v>
+        <v>1526</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1500</v>
+        <v>1527</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K7+Recalculo_Intereses!K8</f>
@@ -7135,18 +7224,18 @@
         <v>1111</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1501</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>1502</v>
+        <v>1529</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1503</v>
+        <v>1530</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>576</v>
@@ -7155,80 +7244,80 @@
         <v>11973677</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1504</v>
+        <v>1531</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>1505</v>
+        <v>1532</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>1478</v>
+        <v>1533</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1506</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>1507</v>
+        <v>1535</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1508</v>
+        <v>1536</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1509</v>
+        <v>1537</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">Clasif_CP_LP!B11+Clasif_CP_LP!B12</f>
         <v>2817285095.14034</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G12" s="46" t="s">
         <v>1510</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G12" s="46" t="s">
-        <v>1478</v>
-      </c>
       <c r="H12" s="10" t="s">
-        <v>1512</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>1513</v>
+        <v>1540</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1514</v>
+        <v>1541</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1515</v>
+        <v>1542</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>1516</v>
+        <v>1543</v>
       </c>
       <c r="G13" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1519</v>
+        <v>1546</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1520</v>
+        <v>1547</v>
       </c>
       <c r="D14" s="11" t="n">
         <f aca="false">SUMIFS(Recalculo_Intereses!K24:K46,Recalculo_Intereses!A24:A46,"BCL-L*")+SUMIFS(Recalculo_Intereses!K24:K46,Recalculo_Intereses!A24:A46,"POP-*")</f>
@@ -7238,53 +7327,53 @@
         <v>930</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>1521</v>
+        <v>1548</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1522</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>1523</v>
+        <v>1550</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1524</v>
+        <v>1551</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1525</v>
+        <v>1552</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1526</v>
+        <v>1553</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>1511</v>
+        <v>1532</v>
       </c>
       <c r="G15" s="46" t="s">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1527</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="19" t="s">
-        <v>1528</v>
+        <v>1555</v>
       </c>
       <c r="D17" s="47" t="n">
-        <f aca="false">COUNTIF(G5:G15,"Pendiente")</f>
+        <f aca="false">COUNTIF(G5:G15,"&lt;&gt;Recibido")</f>
         <v>11</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -34796,12 +34885,11 @@
     <tabColor rgb="FF8EA9DB"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
@@ -34888,7 +34976,7 @@
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="35" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -34928,7 +35016,7 @@
       <c r="M5" s="29" t="n">
         <v>0.1551</v>
       </c>
-      <c r="N5" s="35" t="n">
+      <c r="N5" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E5,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.155893765625</v>
       </c>
@@ -34939,7 +35027,7 @@
       <c r="P5" s="5" t="n">
         <v>52677</v>
       </c>
-      <c r="Q5" s="36" t="n">
+      <c r="Q5" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E5,Detalle_62!$C$14:$C$35,0))</f>
         <v>52677</v>
       </c>
@@ -34947,7 +35035,7 @@
         <f aca="false">IF(P5="","N/D",IF(P5=Q5,"Sí","NO"))</f>
         <v>Sí</v>
       </c>
-      <c r="S5" s="37" t="s">
+      <c r="S5" s="35" t="s">
         <v>1114</v>
       </c>
     </row>
@@ -34955,7 +35043,7 @@
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="35" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="17" t="s">
@@ -34994,7 +35082,7 @@
       <c r="M6" s="29" t="n">
         <v>0.1494</v>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E6,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.158293089495938</v>
       </c>
@@ -35003,7 +35091,7 @@
         <v>88.9308949593778</v>
       </c>
       <c r="P6" s="5"/>
-      <c r="Q6" s="36" t="n">
+      <c r="Q6" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E6,Detalle_62!$C$14:$C$35,0))</f>
         <v>46925</v>
       </c>
@@ -35011,7 +35099,7 @@
         <f aca="false">IF(P6="","N/D",IF(P6=Q6,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S6" s="37" t="s">
+      <c r="S6" s="35" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -35019,7 +35107,7 @@
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="35" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -35058,7 +35146,7 @@
       <c r="M7" s="29" t="n">
         <v>0.1417</v>
       </c>
-      <c r="N7" s="35" t="n">
+      <c r="N7" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E7,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.141053391053319</v>
       </c>
@@ -35069,7 +35157,7 @@
       <c r="P7" s="5" t="n">
         <v>46865</v>
       </c>
-      <c r="Q7" s="36" t="n">
+      <c r="Q7" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E7,Detalle_62!$C$14:$C$35,0))</f>
         <v>46864</v>
       </c>
@@ -35077,7 +35165,7 @@
         <f aca="false">IF(P7="","N/D",IF(P7=Q7,"Sí","NO"))</f>
         <v>NO</v>
       </c>
-      <c r="S7" s="37" t="s">
+      <c r="S7" s="35" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -35085,7 +35173,7 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="35" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="17" t="s">
@@ -35124,7 +35212,7 @@
       <c r="M8" s="29" t="n">
         <v>0.1696</v>
       </c>
-      <c r="N8" s="35" t="n">
+      <c r="N8" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E8,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.175224160801509</v>
       </c>
@@ -35133,7 +35221,7 @@
         <v>56.241608015086</v>
       </c>
       <c r="P8" s="5"/>
-      <c r="Q8" s="36" t="n">
+      <c r="Q8" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E8,Detalle_62!$C$14:$C$35,0))</f>
         <v>47651</v>
       </c>
@@ -35141,7 +35229,7 @@
         <f aca="false">IF(P8="","N/D",IF(P8=Q8,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S8" s="37" t="s">
+      <c r="S8" s="35" t="s">
         <v>1125</v>
       </c>
     </row>
@@ -35149,7 +35237,7 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="35" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -35188,7 +35276,7 @@
       <c r="M9" s="29" t="n">
         <v>0.1665</v>
       </c>
-      <c r="N9" s="35" t="n">
+      <c r="N9" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E9,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.174003555557499</v>
       </c>
@@ -35197,7 +35285,7 @@
         <v>75.0355555749879</v>
       </c>
       <c r="P9" s="5"/>
-      <c r="Q9" s="36" t="n">
+      <c r="Q9" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E9,Detalle_62!$C$14:$C$35,0))</f>
         <v>46990</v>
       </c>
@@ -35205,7 +35293,7 @@
         <f aca="false">IF(P9="","N/D",IF(P9=Q9,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S9" s="37" t="s">
+      <c r="S9" s="35" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -35213,7 +35301,7 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="35" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="17" t="s">
@@ -35252,7 +35340,7 @@
       <c r="M10" s="29" t="n">
         <v>0.1239</v>
       </c>
-      <c r="N10" s="35" t="n">
+      <c r="N10" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E10,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.1296288656</v>
       </c>
@@ -35261,7 +35349,7 @@
         <v>57.2886560000001</v>
       </c>
       <c r="P10" s="5"/>
-      <c r="Q10" s="36" t="n">
+      <c r="Q10" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E10,Detalle_62!$C$14:$C$35,0))</f>
         <v>46409</v>
       </c>
@@ -35269,7 +35357,7 @@
         <f aca="false">IF(P10="","N/D",IF(P10=Q10,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S10" s="37" t="s">
+      <c r="S10" s="35" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -35277,7 +35365,7 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="35" t="n">
         <v>12</v>
       </c>
       <c r="C11" s="17" t="s">
@@ -35317,7 +35405,7 @@
       <c r="M11" s="29" t="n">
         <v>0.1258</v>
       </c>
-      <c r="N11" s="35" t="n">
+      <c r="N11" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E11,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.160198265625</v>
       </c>
@@ -35328,7 +35416,7 @@
       <c r="P11" s="5" t="n">
         <v>51710</v>
       </c>
-      <c r="Q11" s="36" t="n">
+      <c r="Q11" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E11,Detalle_62!$C$14:$C$35,0))</f>
         <v>51710</v>
       </c>
@@ -35336,7 +35424,7 @@
         <f aca="false">IF(P11="","N/D",IF(P11=Q11,"Sí","NO"))</f>
         <v>Sí</v>
       </c>
-      <c r="S11" s="37" t="s">
+      <c r="S11" s="35" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -35344,7 +35432,7 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="35" t="n">
         <v>13</v>
       </c>
       <c r="C12" s="17" t="s">
@@ -35384,7 +35472,7 @@
       <c r="M12" s="29" t="n">
         <v>0.1258</v>
       </c>
-      <c r="N12" s="35" t="n">
+      <c r="N12" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E12,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.160198265625</v>
       </c>
@@ -35395,7 +35483,7 @@
       <c r="P12" s="5" t="n">
         <v>51710</v>
       </c>
-      <c r="Q12" s="36" t="n">
+      <c r="Q12" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E12,Detalle_62!$C$14:$C$35,0))</f>
         <v>51710</v>
       </c>
@@ -35403,7 +35491,7 @@
         <f aca="false">IF(P12="","N/D",IF(P12=Q12,"Sí","NO"))</f>
         <v>Sí</v>
       </c>
-      <c r="S12" s="37" t="s">
+      <c r="S12" s="35" t="s">
         <v>1133</v>
       </c>
     </row>
@@ -35411,20 +35499,20 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="17" t="n">
-        <v>14</v>
+      <c r="B13" s="35" t="s">
+        <v>1134</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>805</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>46209</v>
@@ -35448,7 +35536,7 @@
       <c r="M13" s="29" t="n">
         <v>0.1441</v>
       </c>
-      <c r="N13" s="35" t="n">
+      <c r="N13" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E13,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.148277114550755</v>
       </c>
@@ -35457,7 +35545,7 @@
         <v>41.7711455075528</v>
       </c>
       <c r="P13" s="5"/>
-      <c r="Q13" s="36" t="n">
+      <c r="Q13" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E13,Detalle_62!$C$14:$C$35,0))</f>
         <v>48235</v>
       </c>
@@ -35465,28 +35553,28 @@
         <f aca="false">IF(P13="","N/D",IF(P13=Q13,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S13" s="37" t="s">
-        <v>1137</v>
+      <c r="S13" s="35" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="35" t="n">
         <v>16</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>615</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>46215</v>
@@ -35512,7 +35600,7 @@
       <c r="M14" s="29" t="n">
         <v>0.1604</v>
       </c>
-      <c r="N14" s="35" t="n">
+      <c r="N14" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E14,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.164782455289419</v>
       </c>
@@ -35523,7 +35611,7 @@
       <c r="P14" s="5" t="n">
         <v>47321</v>
       </c>
-      <c r="Q14" s="36" t="n">
+      <c r="Q14" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E14,Detalle_62!$C$14:$C$35,0))</f>
         <v>47321</v>
       </c>
@@ -35531,28 +35619,28 @@
         <f aca="false">IF(P14="","N/D",IF(P14=Q14,"Sí","NO"))</f>
         <v>Sí</v>
       </c>
-      <c r="S14" s="37" t="s">
-        <v>1141</v>
+      <c r="S14" s="35" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="35" t="n">
         <v>17</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>609</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>46220</v>
@@ -35578,7 +35666,7 @@
       <c r="M15" s="29" t="n">
         <v>0.1425</v>
       </c>
-      <c r="N15" s="35" t="n">
+      <c r="N15" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E15,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.145417886389703</v>
       </c>
@@ -35589,7 +35677,7 @@
       <c r="P15" s="5" t="n">
         <v>46961</v>
       </c>
-      <c r="Q15" s="36" t="n">
+      <c r="Q15" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E15,Detalle_62!$C$14:$C$35,0))</f>
         <v>46870</v>
       </c>
@@ -35597,28 +35685,28 @@
         <f aca="false">IF(P15="","N/D",IF(P15=Q15,"Sí","NO"))</f>
         <v>NO</v>
       </c>
-      <c r="S15" s="37" t="s">
-        <v>1143</v>
+      <c r="S15" s="35" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="35" t="n">
         <v>18</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>606</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>46220</v>
@@ -35644,7 +35732,7 @@
       <c r="M16" s="29" t="n">
         <v>0.1425</v>
       </c>
-      <c r="N16" s="35" t="n">
+      <c r="N16" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E16,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.145417886389703</v>
       </c>
@@ -35655,7 +35743,7 @@
       <c r="P16" s="5" t="n">
         <v>46961</v>
       </c>
-      <c r="Q16" s="36" t="n">
+      <c r="Q16" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E16,Detalle_62!$C$14:$C$35,0))</f>
         <v>46870</v>
       </c>
@@ -35663,28 +35751,28 @@
         <f aca="false">IF(P16="","N/D",IF(P16=Q16,"Sí","NO"))</f>
         <v>NO</v>
       </c>
-      <c r="S16" s="37" t="s">
-        <v>1145</v>
+      <c r="S16" s="35" t="s">
+        <v>1146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="35" t="n">
         <v>19</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>618</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>46216</v>
@@ -35710,7 +35798,7 @@
       <c r="M17" s="29" t="n">
         <v>0.1422</v>
       </c>
-      <c r="N17" s="35" t="n">
+      <c r="N17" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E17,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.145417886389703</v>
       </c>
@@ -35721,7 +35809,7 @@
       <c r="P17" s="5" t="n">
         <v>47506</v>
       </c>
-      <c r="Q17" s="36" t="n">
+      <c r="Q17" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E17,Detalle_62!$C$14:$C$35,0))</f>
         <v>47503</v>
       </c>
@@ -35729,28 +35817,28 @@
         <f aca="false">IF(P17="","N/D",IF(P17=Q17,"Sí","NO"))</f>
         <v>NO</v>
       </c>
-      <c r="S17" s="37" t="s">
-        <v>1147</v>
+      <c r="S17" s="35" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="35" t="n">
         <v>20</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>621</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>46216</v>
@@ -35776,7 +35864,7 @@
       <c r="M18" s="29" t="n">
         <v>0.1422</v>
       </c>
-      <c r="N18" s="35" t="n">
+      <c r="N18" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E18,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.145417886389703</v>
       </c>
@@ -35787,7 +35875,7 @@
       <c r="P18" s="5" t="n">
         <v>47506</v>
       </c>
-      <c r="Q18" s="36" t="n">
+      <c r="Q18" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E18,Detalle_62!$C$14:$C$35,0))</f>
         <v>47503</v>
       </c>
@@ -35795,28 +35883,28 @@
         <f aca="false">IF(P18="","N/D",IF(P18=Q18,"Sí","NO"))</f>
         <v>NO</v>
       </c>
-      <c r="S18" s="37" t="s">
-        <v>1149</v>
+      <c r="S18" s="35" t="s">
+        <v>1150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="35" t="n">
         <v>21</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>612</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>46213</v>
@@ -35842,7 +35930,7 @@
       <c r="M19" s="29" t="n">
         <v>0.1422</v>
       </c>
-      <c r="N19" s="35" t="n">
+      <c r="N19" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E19,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.145417886389703</v>
       </c>
@@ -35853,7 +35941,7 @@
       <c r="P19" s="5" t="n">
         <v>47503</v>
       </c>
-      <c r="Q19" s="36" t="n">
+      <c r="Q19" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E19,Detalle_62!$C$14:$C$35,0))</f>
         <v>47503</v>
       </c>
@@ -35861,28 +35949,28 @@
         <f aca="false">IF(P19="","N/D",IF(P19=Q19,"Sí","NO"))</f>
         <v>Sí</v>
       </c>
-      <c r="S19" s="37" t="s">
-        <v>1151</v>
+      <c r="S19" s="35" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="17" t="n">
-        <v>22</v>
+      <c r="B20" s="35" t="s">
+        <v>1153</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>576</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>46198</v>
@@ -35906,7 +35994,7 @@
       <c r="M20" s="29" t="n">
         <v>0.1603</v>
       </c>
-      <c r="N20" s="35" t="n">
+      <c r="N20" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E20,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.167133181668336</v>
       </c>
@@ -35915,7 +36003,7 @@
         <v>68.3318166833549</v>
       </c>
       <c r="P20" s="5"/>
-      <c r="Q20" s="36" t="n">
+      <c r="Q20" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E20,Detalle_62!$C$14:$C$35,0))</f>
         <v>47037</v>
       </c>
@@ -35923,28 +36011,28 @@
         <f aca="false">IF(P20="","N/D",IF(P20=Q20,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S20" s="37" t="s">
-        <v>1153</v>
+      <c r="S20" s="35" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="17" t="n">
-        <v>24</v>
+      <c r="B21" s="35" t="s">
+        <v>1156</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>572</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>46191</v>
@@ -35968,7 +36056,7 @@
       <c r="M21" s="29" t="n">
         <v>0.1593</v>
       </c>
-      <c r="N21" s="35" t="n">
+      <c r="N21" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH(E21,Detalle_62!$C$14:$C$35,0))</f>
         <v>0.167133181668336</v>
       </c>
@@ -35977,7 +36065,7 @@
         <v>78.3318166833549</v>
       </c>
       <c r="P21" s="5"/>
-      <c r="Q21" s="36" t="n">
+      <c r="Q21" s="37" t="n">
         <f aca="false">INDEX(Detalle_62!$P$14:$P$35,MATCH(E21,Detalle_62!$C$14:$C$35,0))</f>
         <v>47098</v>
       </c>
@@ -35985,13 +36073,13 @@
         <f aca="false">IF(P21="","N/D",IF(P21=Q21,"Sí","NO"))</f>
         <v>N/D</v>
       </c>
-      <c r="S21" s="37" t="s">
-        <v>1155</v>
+      <c r="S21" s="35" t="s">
+        <v>1158</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F22" s="19" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="J22" s="20" t="n">
         <f aca="false">SUMIFS(J5:J21,$H$5:$H$21,"&lt;&gt;")</f>
@@ -36008,7 +36096,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F23" s="4" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="L23" s="38" t="n">
         <f aca="false">SUMIFS(L5:L21,E5:E21,"BOG-L*")</f>
@@ -36017,7 +36105,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F24" s="4" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">L22-L23</f>
@@ -36026,7 +36114,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -36054,7 +36142,7 @@
         <v>1019</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>1021</v>
@@ -36093,7 +36181,7 @@
         <v>1074</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>91</v>
@@ -36165,7 +36253,7 @@
         <v>1119</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>552</v>
@@ -36180,7 +36268,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F34" s="19" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="K34" s="20" t="n">
         <f aca="false">SUM(K28:K32)</f>
@@ -36189,7 +36277,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F35" s="4" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="K35" s="15" t="n">
         <f aca="false">1-K34/Detalle_62!$F$36</f>
@@ -36198,7 +36286,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -36229,17 +36317,17 @@
         <v>987</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>74</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>12</v>
@@ -36260,13 +36348,13 @@
       <c r="C39" s="13" t="s">
         <v>707</v>
       </c>
-      <c r="D39" s="37" t="s">
-        <v>1169</v>
+      <c r="D39" s="35" t="s">
+        <v>1172</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>727</v>
       </c>
-      <c r="F39" s="36" t="n">
+      <c r="F39" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E39,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46105</v>
       </c>
@@ -36281,21 +36369,21 @@
         <f aca="false">I39-H39</f>
         <v>0</v>
       </c>
-      <c r="S39" s="37" t="s">
-        <v>1170</v>
+      <c r="S39" s="35" t="s">
+        <v>1173</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C40" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="D40" s="37" t="s">
-        <v>1171</v>
+      <c r="D40" s="35" t="s">
+        <v>1174</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>713</v>
       </c>
-      <c r="F40" s="36" t="n">
+      <c r="F40" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E40,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46051</v>
       </c>
@@ -36310,21 +36398,21 @@
         <f aca="false">I40-H40</f>
         <v>0</v>
       </c>
-      <c r="S40" s="37" t="s">
-        <v>1172</v>
+      <c r="S40" s="35" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C41" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="D41" s="37" t="s">
-        <v>1173</v>
+      <c r="D41" s="35" t="s">
+        <v>1176</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>715</v>
       </c>
-      <c r="F41" s="36" t="n">
+      <c r="F41" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E41,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46051</v>
       </c>
@@ -36339,21 +36427,21 @@
         <f aca="false">I41-H41</f>
         <v>0</v>
       </c>
-      <c r="S41" s="37" t="s">
-        <v>1174</v>
+      <c r="S41" s="35" t="s">
+        <v>1177</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C42" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="D42" s="37" t="s">
-        <v>1175</v>
+      <c r="D42" s="35" t="s">
+        <v>1178</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>742</v>
       </c>
-      <c r="F42" s="36" t="n">
+      <c r="F42" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E42,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -36368,21 +36456,21 @@
         <f aca="false">I42-H42</f>
         <v>617.949999988079</v>
       </c>
-      <c r="S42" s="37" t="s">
-        <v>1176</v>
+      <c r="S42" s="35" t="s">
+        <v>1179</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C43" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="D43" s="37" t="s">
-        <v>1175</v>
+      <c r="D43" s="35" t="s">
+        <v>1178</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="F43" s="36" t="n">
+      <c r="F43" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E43,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -36397,21 +36485,21 @@
         <f aca="false">I43-H43</f>
         <v>786.800000011921</v>
       </c>
-      <c r="S43" s="37" t="s">
-        <v>1177</v>
+      <c r="S43" s="35" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C44" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="37" t="s">
-        <v>1178</v>
+      <c r="D44" s="35" t="s">
+        <v>1181</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F44" s="36" t="n">
+      <c r="F44" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E44,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46100</v>
       </c>
@@ -36426,21 +36514,21 @@
         <f aca="false">I44-H44</f>
         <v>-0.530000001192093</v>
       </c>
-      <c r="S44" s="37" t="s">
-        <v>1179</v>
+      <c r="S44" s="35" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C45" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="37" t="s">
-        <v>1180</v>
+      <c r="D45" s="35" t="s">
+        <v>1183</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="F45" s="36" t="n">
+      <c r="F45" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E45,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46100</v>
       </c>
@@ -36455,19 +36543,19 @@
         <f aca="false">I45-H45</f>
         <v>-0.469999998807907</v>
       </c>
-      <c r="S45" s="37"/>
+      <c r="S45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C46" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="37" t="s">
-        <v>1181</v>
+      <c r="D46" s="35" t="s">
+        <v>1184</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F46" s="36" t="n">
+      <c r="F46" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E46,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46197</v>
       </c>
@@ -36482,19 +36570,19 @@
         <f aca="false">I46-H46</f>
         <v>0</v>
       </c>
-      <c r="S46" s="37"/>
+      <c r="S46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C47" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="37" t="s">
-        <v>1182</v>
+      <c r="D47" s="35" t="s">
+        <v>1185</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>768</v>
       </c>
-      <c r="F47" s="36" t="n">
+      <c r="F47" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E47,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46203</v>
       </c>
@@ -36509,19 +36597,19 @@
         <f aca="false">I47-H47</f>
         <v>-0.229999996721745</v>
       </c>
-      <c r="S47" s="37"/>
+      <c r="S47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C48" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="37" t="s">
-        <v>1183</v>
+      <c r="D48" s="35" t="s">
+        <v>1186</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F48" s="36" t="n">
+      <c r="F48" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E48,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46197</v>
       </c>
@@ -36536,19 +36624,19 @@
         <f aca="false">I48-H48</f>
         <v>-0.0900000035762787</v>
       </c>
-      <c r="S48" s="37"/>
+      <c r="S48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C49" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="37" t="s">
-        <v>1184</v>
+      <c r="D49" s="35" t="s">
+        <v>1187</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F49" s="36" t="n">
+      <c r="F49" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E49,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46230</v>
       </c>
@@ -36563,21 +36651,21 @@
         <f aca="false">I49-H49</f>
         <v>0</v>
       </c>
-      <c r="S49" s="37" t="s">
-        <v>1185</v>
+      <c r="S49" s="35" t="s">
+        <v>1188</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C50" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D50" s="37" t="s">
-        <v>1186</v>
+      <c r="D50" s="35" t="s">
+        <v>1189</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F50" s="36" t="n">
+      <c r="F50" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E50,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46164</v>
       </c>
@@ -36592,19 +36680,19 @@
         <f aca="false">I50-H50</f>
         <v>-0.560000002384186</v>
       </c>
-      <c r="S50" s="37"/>
+      <c r="S50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C51" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D51" s="37" t="s">
-        <v>1187</v>
+      <c r="D51" s="35" t="s">
+        <v>1190</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>766</v>
       </c>
-      <c r="F51" s="36" t="n">
+      <c r="F51" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E51,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46164</v>
       </c>
@@ -36619,19 +36707,19 @@
         <f aca="false">I51-H51</f>
         <v>-0.439999997615814</v>
       </c>
-      <c r="S51" s="37"/>
+      <c r="S51" s="35"/>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C52" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="37" t="s">
-        <v>1188</v>
+      <c r="D52" s="35" t="s">
+        <v>1191</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>761</v>
       </c>
-      <c r="F52" s="36" t="n">
+      <c r="F52" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E52,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -36646,19 +36734,19 @@
         <f aca="false">I52-H52</f>
         <v>0.449999988079071</v>
       </c>
-      <c r="S52" s="37"/>
+      <c r="S52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C53" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D53" s="37" t="s">
-        <v>1189</v>
+      <c r="D53" s="35" t="s">
+        <v>1192</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>776</v>
       </c>
-      <c r="F53" s="36" t="n">
+      <c r="F53" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E53,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46230</v>
       </c>
@@ -36673,19 +36761,19 @@
         <f aca="false">I53-H53</f>
         <v>-1</v>
       </c>
-      <c r="S53" s="37"/>
+      <c r="S53" s="35"/>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C54" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="D54" s="37" t="s">
-        <v>1190</v>
+      <c r="D54" s="35" t="s">
+        <v>1193</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>626</v>
       </c>
-      <c r="F54" s="36" t="n">
+      <c r="F54" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E54,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -36700,19 +36788,19 @@
         <f aca="false">I54-H54</f>
         <v>0</v>
       </c>
-      <c r="S54" s="37"/>
+      <c r="S54" s="35"/>
     </row>
     <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C55" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="D55" s="37" t="s">
-        <v>1191</v>
+      <c r="D55" s="35" t="s">
+        <v>1194</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>859</v>
       </c>
-      <c r="F55" s="36" t="n">
+      <c r="F55" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E55,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -36727,19 +36815,19 @@
         <f aca="false">I55-H55</f>
         <v>-0.969999998807907</v>
       </c>
-      <c r="S55" s="37"/>
+      <c r="S55" s="35"/>
     </row>
     <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C56" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="D56" s="37" t="s">
-        <v>1192</v>
+      <c r="D56" s="35" t="s">
+        <v>1195</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>642</v>
       </c>
-      <c r="F56" s="36" t="n">
+      <c r="F56" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E56,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -36754,19 +36842,19 @@
         <f aca="false">I56-H56</f>
         <v>0</v>
       </c>
-      <c r="S56" s="37"/>
+      <c r="S56" s="35"/>
     </row>
     <row r="57" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C57" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="D57" s="37" t="s">
-        <v>1193</v>
+      <c r="D57" s="35" t="s">
+        <v>1196</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>893</v>
       </c>
-      <c r="F57" s="36" t="n">
+      <c r="F57" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E57,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -36781,19 +36869,19 @@
         <f aca="false">I57-H57</f>
         <v>-0.880000002682209</v>
       </c>
-      <c r="S57" s="37"/>
+      <c r="S57" s="35"/>
     </row>
     <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C58" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="D58" s="37" t="s">
-        <v>1190</v>
+      <c r="D58" s="35" t="s">
+        <v>1193</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>632</v>
       </c>
-      <c r="F58" s="36" t="n">
+      <c r="F58" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E58,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -36808,19 +36896,19 @@
         <f aca="false">I58-H58</f>
         <v>0</v>
       </c>
-      <c r="S58" s="37"/>
+      <c r="S58" s="35"/>
     </row>
     <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C59" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="D59" s="37" t="s">
-        <v>1192</v>
+      <c r="D59" s="35" t="s">
+        <v>1195</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>636</v>
       </c>
-      <c r="F59" s="36" t="n">
+      <c r="F59" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E59,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46230</v>
       </c>
@@ -36835,19 +36923,19 @@
         <f aca="false">I59-H59</f>
         <v>0</v>
       </c>
-      <c r="S59" s="37"/>
+      <c r="S59" s="35"/>
     </row>
     <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C60" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="D60" s="37" t="s">
-        <v>1193</v>
+      <c r="D60" s="35" t="s">
+        <v>1196</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>887</v>
       </c>
-      <c r="F60" s="36" t="n">
+      <c r="F60" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E60,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46230</v>
       </c>
@@ -36862,19 +36950,19 @@
         <f aca="false">I60-H60</f>
         <v>-0.300000000745058</v>
       </c>
-      <c r="S60" s="37"/>
+      <c r="S60" s="35"/>
     </row>
     <row r="61" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C61" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="D61" s="37" t="s">
-        <v>1190</v>
+      <c r="D61" s="35" t="s">
+        <v>1193</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>622</v>
       </c>
-      <c r="F61" s="36" t="n">
+      <c r="F61" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E61,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -36889,19 +36977,19 @@
         <f aca="false">I61-H61</f>
         <v>0</v>
       </c>
-      <c r="S61" s="37"/>
+      <c r="S61" s="35"/>
     </row>
     <row r="62" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C62" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="D62" s="37" t="s">
-        <v>1192</v>
+      <c r="D62" s="35" t="s">
+        <v>1195</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>634</v>
       </c>
-      <c r="F62" s="36" t="n">
+      <c r="F62" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E62,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46230</v>
       </c>
@@ -36916,19 +37004,19 @@
         <f aca="false">I62-H62</f>
         <v>0</v>
       </c>
-      <c r="S62" s="37"/>
+      <c r="S62" s="35"/>
     </row>
     <row r="63" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C63" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="D63" s="37" t="s">
-        <v>1193</v>
+      <c r="D63" s="35" t="s">
+        <v>1196</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="F63" s="36" t="n">
+      <c r="F63" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E63,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46230</v>
       </c>
@@ -36943,19 +37031,19 @@
         <f aca="false">I63-H63</f>
         <v>-0.28999999910593</v>
       </c>
-      <c r="S63" s="37"/>
+      <c r="S63" s="35"/>
     </row>
     <row r="64" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C64" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="D64" s="37" t="s">
-        <v>1190</v>
+      <c r="D64" s="35" t="s">
+        <v>1193</v>
       </c>
       <c r="E64" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="F64" s="36" t="n">
+      <c r="F64" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E64,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -36970,19 +37058,19 @@
         <f aca="false">I64-H64</f>
         <v>0</v>
       </c>
-      <c r="S64" s="37"/>
+      <c r="S64" s="35"/>
     </row>
     <row r="65" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C65" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="D65" s="37" t="s">
-        <v>1192</v>
+      <c r="D65" s="35" t="s">
+        <v>1195</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>640</v>
       </c>
-      <c r="F65" s="36" t="n">
+      <c r="F65" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E65,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -36997,19 +37085,19 @@
         <f aca="false">I65-H65</f>
         <v>0</v>
       </c>
-      <c r="S65" s="37"/>
+      <c r="S65" s="35"/>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C66" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="D66" s="37" t="s">
-        <v>1193</v>
+      <c r="D66" s="35" t="s">
+        <v>1196</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>891</v>
       </c>
-      <c r="F66" s="36" t="n">
+      <c r="F66" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E66,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37024,19 +37112,19 @@
         <f aca="false">I66-H66</f>
         <v>-0.990000000223517</v>
       </c>
-      <c r="S66" s="37"/>
+      <c r="S66" s="35"/>
     </row>
     <row r="67" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C67" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="D67" s="37" t="s">
-        <v>1190</v>
+      <c r="D67" s="35" t="s">
+        <v>1193</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>630</v>
       </c>
-      <c r="F67" s="36" t="n">
+      <c r="F67" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E67,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -37051,21 +37139,21 @@
         <f aca="false">I67-H67</f>
         <v>0</v>
       </c>
-      <c r="S67" s="37" t="s">
-        <v>1194</v>
+      <c r="S67" s="35" t="s">
+        <v>1197</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C68" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="D68" s="37" t="s">
-        <v>1192</v>
+      <c r="D68" s="35" t="s">
+        <v>1195</v>
       </c>
       <c r="E68" s="17" t="s">
         <v>638</v>
       </c>
-      <c r="F68" s="36" t="n">
+      <c r="F68" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E68,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37080,19 +37168,19 @@
         <f aca="false">I68-H68</f>
         <v>0</v>
       </c>
-      <c r="S68" s="37"/>
+      <c r="S68" s="35"/>
     </row>
     <row r="69" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C69" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="D69" s="37" t="s">
-        <v>1193</v>
+      <c r="D69" s="35" t="s">
+        <v>1196</v>
       </c>
       <c r="E69" s="17" t="s">
         <v>889</v>
       </c>
-      <c r="F69" s="36" t="n">
+      <c r="F69" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E69,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37107,19 +37195,19 @@
         <f aca="false">I69-H69</f>
         <v>-1.98000000044703</v>
       </c>
-      <c r="S69" s="37"/>
+      <c r="S69" s="35"/>
     </row>
     <row r="70" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C70" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="D70" s="37" t="s">
-        <v>1190</v>
+      <c r="D70" s="35" t="s">
+        <v>1193</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>624</v>
       </c>
-      <c r="F70" s="36" t="n">
+      <c r="F70" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E70,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -37134,19 +37222,19 @@
         <f aca="false">I70-H70</f>
         <v>0</v>
       </c>
-      <c r="S70" s="37"/>
+      <c r="S70" s="35"/>
     </row>
     <row r="71" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C71" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="D71" s="37" t="s">
-        <v>1192</v>
+      <c r="D71" s="35" t="s">
+        <v>1195</v>
       </c>
       <c r="E71" s="17" t="s">
         <v>644</v>
       </c>
-      <c r="F71" s="36" t="n">
+      <c r="F71" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E71,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37161,19 +37249,19 @@
         <f aca="false">I71-H71</f>
         <v>0</v>
       </c>
-      <c r="S71" s="37"/>
+      <c r="S71" s="35"/>
     </row>
     <row r="72" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C72" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="D72" s="37" t="s">
-        <v>1193</v>
+      <c r="D72" s="35" t="s">
+        <v>1196</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>895</v>
       </c>
-      <c r="F72" s="36" t="n">
+      <c r="F72" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E72,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37188,19 +37276,19 @@
         <f aca="false">I72-H72</f>
         <v>0</v>
       </c>
-      <c r="S72" s="37"/>
+      <c r="S72" s="35"/>
     </row>
     <row r="73" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C73" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="D73" s="37" t="s">
-        <v>1195</v>
+      <c r="D73" s="35" t="s">
+        <v>1198</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>812</v>
       </c>
-      <c r="F73" s="36" t="n">
+      <c r="F73" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E73,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46136</v>
       </c>
@@ -37215,19 +37303,19 @@
         <f aca="false">I73-H73</f>
         <v>0</v>
       </c>
-      <c r="S73" s="37"/>
+      <c r="S73" s="35"/>
     </row>
     <row r="74" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C74" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="D74" s="37" t="s">
-        <v>1196</v>
+      <c r="D74" s="35" t="s">
+        <v>1199</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>817</v>
       </c>
-      <c r="F74" s="36" t="n">
+      <c r="F74" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E74,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37242,19 +37330,19 @@
         <f aca="false">I74-H74</f>
         <v>-1</v>
       </c>
-      <c r="S74" s="37"/>
+      <c r="S74" s="35"/>
     </row>
     <row r="75" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C75" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="D75" s="37" t="s">
-        <v>1197</v>
+      <c r="D75" s="35" t="s">
+        <v>1200</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>593</v>
       </c>
-      <c r="F75" s="36" t="n">
+      <c r="F75" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E75,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46203</v>
       </c>
@@ -37269,19 +37357,19 @@
         <f aca="false">I75-H75</f>
         <v>0</v>
       </c>
-      <c r="S75" s="37"/>
+      <c r="S75" s="35"/>
     </row>
     <row r="76" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C76" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="D76" s="37" t="s">
-        <v>1198</v>
+      <c r="D76" s="35" t="s">
+        <v>1201</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>600</v>
       </c>
-      <c r="F76" s="36" t="n">
+      <c r="F76" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E76,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37296,19 +37384,19 @@
         <f aca="false">I76-H76</f>
         <v>0</v>
       </c>
-      <c r="S76" s="37"/>
+      <c r="S76" s="35"/>
     </row>
     <row r="77" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C77" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="D77" s="37" t="s">
-        <v>1199</v>
+      <c r="D77" s="35" t="s">
+        <v>1202</v>
       </c>
       <c r="E77" s="17" t="s">
         <v>595</v>
       </c>
-      <c r="F77" s="36" t="n">
+      <c r="F77" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E77,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46203</v>
       </c>
@@ -37323,21 +37411,21 @@
         <f aca="false">I77-H77</f>
         <v>11973677</v>
       </c>
-      <c r="S77" s="37" t="s">
-        <v>1200</v>
+      <c r="S77" s="35" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C78" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="D78" s="37" t="s">
-        <v>1201</v>
+      <c r="D78" s="35" t="s">
+        <v>1204</v>
       </c>
       <c r="E78" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="F78" s="36" t="n">
+      <c r="F78" s="37" t="n">
         <f aca="false">INDEX(Mayor_Mov!$H$5:$H$445,MATCH(E78,Mayor_Mov!$J$5:$J$445,0))</f>
         <v>46231</v>
       </c>
@@ -37352,11 +37440,11 @@
         <f aca="false">I78-H78</f>
         <v>0</v>
       </c>
-      <c r="S78" s="37"/>
+      <c r="S78" s="35"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D79" s="19" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="H79" s="20" t="n">
         <f aca="false">SUM(H39:H78)</f>
@@ -37369,6 +37457,241 @@
       <c r="J79" s="20" t="n">
         <f aca="false">SUM(J39:J78)</f>
         <v>11975072.47</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="25" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+      <c r="Q81" s="26"/>
+      <c r="R81" s="26"/>
+      <c r="S81" s="26"/>
+    </row>
+    <row r="82" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="9"/>
+      <c r="B82" s="9" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>1212</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K82" s="9" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>1215</v>
+      </c>
+      <c r="M82" s="9" t="s">
+        <v>1216</v>
+      </c>
+      <c r="N82" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="O82" s="9" t="s">
+        <v>1218</v>
+      </c>
+      <c r="P82" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="Q82" s="9"/>
+      <c r="R82" s="9"/>
+      <c r="S82" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="35" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>805</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F83" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="18" t="n">
+        <v>64041851</v>
+      </c>
+      <c r="I83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="29" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>46135</v>
+      </c>
+      <c r="L83" s="18" t="n">
+        <v>55427870</v>
+      </c>
+      <c r="M83" s="39" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N83" s="23" t="str">
+        <f aca="false">IF(H83=Recalculo_Intereses!C55,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="O83" s="23" t="str">
+        <f aca="false">IF(G83=Recalculo_Intereses!I55,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="P83" s="4" t="str">
+        <f aca="false">IF(J83=M13,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="S83" s="35" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="35" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G84" s="18" t="n">
+        <v>12327298</v>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>5062372</v>
+      </c>
+      <c r="I84" s="18" t="n">
+        <v>1263646</v>
+      </c>
+      <c r="J84" s="29" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="L84" s="18" t="n">
+        <v>1029562</v>
+      </c>
+      <c r="M84" s="39" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N84" s="23" t="str">
+        <f aca="false">IF(H84=Recalculo_Intereses!C56,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="O84" s="23" t="str">
+        <f aca="false">IF(G84=Recalculo_Intereses!I56,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="P84" s="4" t="str">
+        <f aca="false">IF(J84=M20,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="S84" s="35" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="35" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>46191</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G85" s="18" t="n">
+        <v>8867342</v>
+      </c>
+      <c r="H85" s="18" t="n">
+        <v>4177893</v>
+      </c>
+      <c r="I85" s="18" t="n">
+        <v>1263646</v>
+      </c>
+      <c r="J85" s="29" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>46178</v>
+      </c>
+      <c r="L85" s="18" t="n">
+        <v>14567863</v>
+      </c>
+      <c r="M85" s="39" t="s">
+        <v>1222</v>
+      </c>
+      <c r="N85" s="23" t="str">
+        <f aca="false">IF(H85=Recalculo_Intereses!C57,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="O85" s="23" t="str">
+        <f aca="false">IF(G85=Recalculo_Intereses!I57,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="P85" s="4" t="str">
+        <f aca="false">IF(J85=M21,"Sí","NO")</f>
+        <v>Sí</v>
+      </c>
+      <c r="S85" s="35" t="s">
+        <v>1223</v>
       </c>
     </row>
   </sheetData>
@@ -37401,17 +37724,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1203</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1204</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1205</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37419,17 +37742,17 @@
         <v>987</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1206</v>
+        <v>1232</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
         <v>1103</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1207</v>
+        <v>1233</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1208</v>
+        <v>1234</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>13</v>
@@ -37437,10 +37760,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="D6" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$D$14:$D$35,"Crédito")</f>
@@ -37461,10 +37784,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1211</v>
+        <v>1237</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1212</v>
+        <v>1238</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$D$14:$D$35,"Leasing")</f>
@@ -37485,7 +37808,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">D6+D7</f>
@@ -37506,7 +37829,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>1213</v>
+        <v>1239</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">Detalle_62!F36-D8</f>
@@ -37515,34 +37838,34 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>1214</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>1215</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>1216</v>
+        <v>1242</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>1217</v>
+        <v>1243</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>1218</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1219</v>
+        <v>1245</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -37553,12 +37876,12 @@
         <v>675837500</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>1220</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1221</v>
+        <v>1247</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -37569,12 +37892,12 @@
         <v>171608254.364557</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>1222</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1223</v>
+        <v>1249</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -37585,12 +37908,12 @@
         <v>170820422.336308</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>1224</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>1225</v>
+        <v>1251</v>
       </c>
       <c r="F17" s="20" t="n">
         <f aca="false">SUM(F14:F16)</f>
@@ -37603,7 +37926,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>1226</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37617,19 +37940,19 @@
         <v>1022</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1227</v>
+        <v>1253</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>1228</v>
+        <v>1254</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>1229</v>
+        <v>1255</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>1230</v>
+        <v>1256</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>1231</v>
+        <v>1257</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>993</v>
@@ -37665,7 +37988,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A21)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I21" s="37"/>
+      <c r="I21" s="35"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
@@ -37697,7 +38020,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A22)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I22" s="37"/>
+      <c r="I22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
@@ -37729,7 +38052,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A23)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I23" s="37"/>
+      <c r="I23" s="35"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
@@ -37761,7 +38084,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A24)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I24" s="37"/>
+      <c r="I24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
@@ -37793,7 +38116,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A25)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I25" s="37"/>
+      <c r="I25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
@@ -37825,7 +38148,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A26)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I26" s="37"/>
+      <c r="I26" s="35"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
@@ -37857,7 +38180,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A27)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I27" s="37"/>
+      <c r="I27" s="35"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
@@ -37889,7 +38212,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A28)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I28" s="37"/>
+      <c r="I28" s="35"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
@@ -37921,7 +38244,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A29)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I29" s="37"/>
+      <c r="I29" s="35"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
@@ -37953,8 +38276,8 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A30)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I30" s="37" t="s">
-        <v>1232</v>
+      <c r="I30" s="35" t="s">
+        <v>1258</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37987,7 +38310,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A31)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I31" s="37"/>
+      <c r="I31" s="35"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
@@ -38019,7 +38342,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A32)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I32" s="37"/>
+      <c r="I32" s="35"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
@@ -38051,7 +38374,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A33)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I33" s="37"/>
+      <c r="I33" s="35"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
@@ -38083,7 +38406,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A34)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I34" s="37"/>
+      <c r="I34" s="35"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
@@ -38115,7 +38438,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A35)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I35" s="37"/>
+      <c r="I35" s="35"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
@@ -38147,7 +38470,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A36)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I36" s="37"/>
+      <c r="I36" s="35"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
@@ -38179,7 +38502,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A37)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I37" s="37"/>
+      <c r="I37" s="35"/>
     </row>
     <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
@@ -38211,8 +38534,8 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A38)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I38" s="37" t="s">
-        <v>1233</v>
+      <c r="I38" s="35" t="s">
+        <v>1259</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38245,8 +38568,8 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A39)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I39" s="37" t="s">
-        <v>1234</v>
+      <c r="I39" s="35" t="s">
+        <v>1260</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38279,7 +38602,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A40)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I40" s="37"/>
+      <c r="I40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
@@ -38311,7 +38634,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A41)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I41" s="37"/>
+      <c r="I41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
@@ -38343,7 +38666,7 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A42)&gt;0,"Sí","NO")</f>
         <v>Sí</v>
       </c>
-      <c r="I42" s="37"/>
+      <c r="I42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
@@ -38375,8 +38698,8 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A43)&gt;0,"Sí","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I43" s="37" t="s">
-        <v>1235</v>
+      <c r="I43" s="35" t="s">
+        <v>1261</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38409,8 +38732,8 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A44)&gt;0,"Sí","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I44" s="37" t="s">
-        <v>1236</v>
+      <c r="I44" s="35" t="s">
+        <v>1262</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38418,7 +38741,7 @@
         <v>558</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>1237</v>
+        <v>1263</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>1045</v>
@@ -38443,8 +38766,8 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A45)&gt;0,"Sí","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I45" s="37" t="s">
-        <v>1238</v>
+      <c r="I45" s="35" t="s">
+        <v>1264</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38452,7 +38775,7 @@
         <v>599</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>1237</v>
+        <v>1263</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>1045</v>
@@ -38477,13 +38800,13 @@
         <f aca="false">IF(COUNTIF(Detalle_62!$C$14:$C$35,A46)&gt;0,"Sí","NO")</f>
         <v>NO</v>
       </c>
-      <c r="I46" s="37" t="s">
-        <v>1239</v>
+      <c r="I46" s="35" t="s">
+        <v>1265</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>1240</v>
+        <v>1266</v>
       </c>
       <c r="D47" s="20" t="n">
         <f aca="false">SUMIFS(D21:D46,$C$21:$C$46,"Crédito")</f>
@@ -38504,7 +38827,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>1241</v>
+        <v>1267</v>
       </c>
       <c r="E48" s="11" t="n">
         <f aca="false">Balance_21!$D$16+Balance_21!$D$18</f>
@@ -38521,7 +38844,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>1242</v>
+        <v>1268</v>
       </c>
       <c r="E49" s="12" t="n">
         <f aca="false">E47-E48</f>
@@ -38538,7 +38861,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>1243</v>
+        <v>1269</v>
       </c>
       <c r="D51" s="20" t="n">
         <f aca="false">SUMIFS(D21:D46,$C$21:$C$46,"Leasing")</f>
@@ -38559,7 +38882,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>1244</v>
+        <v>1270</v>
       </c>
       <c r="E52" s="11" t="n">
         <f aca="false">Balance_21!$D$22+Balance_21!$D$24</f>
@@ -38576,7 +38899,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>1245</v>
+        <v>1271</v>
       </c>
       <c r="E53" s="12" t="n">
         <f aca="false">E51-E52</f>
@@ -38631,17 +38954,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1246</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1247</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1248</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38649,40 +38972,40 @@
         <v>1021</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1249</v>
+        <v>1275</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1250</v>
+        <v>1276</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1251</v>
+        <v>1277</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1252</v>
+        <v>1278</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1253</v>
+        <v>1279</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>1254</v>
+        <v>1280</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1255</v>
+        <v>1281</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>1256</v>
+        <v>1282</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>1257</v>
+        <v>1283</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>1258</v>
+        <v>1284</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>1259</v>
+        <v>1285</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>1260</v>
+        <v>1286</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>35</v>
@@ -38695,8 +39018,8 @@
       <c r="A6" s="13" t="s">
         <v>707</v>
       </c>
-      <c r="B6" s="37" t="s">
-        <v>1261</v>
+      <c r="B6" s="35" t="s">
+        <v>1287</v>
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">Certificados!J5</f>
@@ -38711,7 +39034,7 @@
       <c r="F6" s="5" t="n">
         <v>46286</v>
       </c>
-      <c r="G6" s="39" t="n">
+      <c r="G6" s="40" t="n">
         <f aca="false">F6-E6</f>
         <v>184</v>
       </c>
@@ -38742,14 +39065,14 @@
         <f aca="false">IF(ABS(L6)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O6" s="37"/>
+      <c r="O6" s="35"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="B7" s="37" t="s">
-        <v>1262</v>
+      <c r="B7" s="35" t="s">
+        <v>1288</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">Certificados!H11</f>
@@ -38764,7 +39087,7 @@
       <c r="F7" s="5" t="n">
         <v>46231</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="40" t="n">
         <f aca="false">F7-E7</f>
         <v>181</v>
       </c>
@@ -38795,16 +39118,16 @@
         <f aca="false">IF(ABS(L7)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Diferencia</v>
       </c>
-      <c r="O7" s="37" t="s">
-        <v>1263</v>
+      <c r="O7" s="35" t="s">
+        <v>1289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="B8" s="37" t="s">
-        <v>1262</v>
+      <c r="B8" s="35" t="s">
+        <v>1288</v>
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">Certificados!H12</f>
@@ -38819,7 +39142,7 @@
       <c r="F8" s="5" t="n">
         <v>46231</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="40" t="n">
         <f aca="false">F8-E8</f>
         <v>181</v>
       </c>
@@ -38850,16 +39173,16 @@
         <f aca="false">IF(ABS(L8)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Diferencia</v>
       </c>
-      <c r="O8" s="37" t="s">
-        <v>1264</v>
+      <c r="O8" s="35" t="s">
+        <v>1290</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="37" t="s">
-        <v>1265</v>
+      <c r="B9" s="35" t="s">
+        <v>1291</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>1639499992.59</v>
@@ -38873,7 +39196,7 @@
       <c r="F9" s="5" t="n">
         <v>46194</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="40" t="n">
         <f aca="false">F9-E9</f>
         <v>92</v>
       </c>
@@ -38904,16 +39227,16 @@
         <f aca="false">IF(ABS(L9)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O9" s="37" t="s">
-        <v>1266</v>
+      <c r="O9" s="35" t="s">
+        <v>1292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="37" t="s">
-        <v>1267</v>
+      <c r="B10" s="35" t="s">
+        <v>1293</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">Certificados!H9</f>
@@ -38928,7 +39251,7 @@
       <c r="F10" s="5" t="n">
         <v>46259</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="40" t="n">
         <f aca="false">F10-E10</f>
         <v>92</v>
       </c>
@@ -38959,16 +39282,16 @@
         <f aca="false">IF(ABS(L10)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O10" s="37" t="s">
-        <v>1268</v>
+      <c r="O10" s="35" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="37" t="s">
-        <v>1269</v>
+      <c r="B11" s="35" t="s">
+        <v>1295</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">Certificados!H8</f>
@@ -38983,7 +39306,7 @@
       <c r="F11" s="5" t="n">
         <v>46220</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="40" t="n">
         <f aca="false">F11-E11</f>
         <v>30</v>
       </c>
@@ -39014,16 +39337,16 @@
         <f aca="false">IF(ABS(L11)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O11" s="37" t="s">
-        <v>1270</v>
+      <c r="O11" s="35" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="37" t="s">
-        <v>1271</v>
+      <c r="B12" s="35" t="s">
+        <v>1297</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>10000000000</v>
@@ -39037,7 +39360,7 @@
       <c r="F12" s="5" t="n">
         <v>46217</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="40" t="n">
         <f aca="false">F12-E12</f>
         <v>91</v>
       </c>
@@ -39068,16 +39391,16 @@
         <f aca="false">IF(ABS(L12)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O12" s="37" t="s">
-        <v>1268</v>
+      <c r="O12" s="35" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>1272</v>
+      <c r="B13" s="35" t="s">
+        <v>1298</v>
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">Certificados!H7</f>
@@ -39092,7 +39415,7 @@
       <c r="F13" s="5" t="n">
         <v>46245</v>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G13" s="40" t="n">
         <f aca="false">F13-E13</f>
         <v>20</v>
       </c>
@@ -39123,14 +39446,14 @@
         <f aca="false">IF(ABS(L13)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O13" s="37"/>
+      <c r="O13" s="35"/>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>615</v>
       </c>
-      <c r="B14" s="37" t="s">
-        <v>1273</v>
+      <c r="B14" s="35" t="s">
+        <v>1299</v>
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">Certificados!H14</f>
@@ -39145,7 +39468,7 @@
       <c r="F14" s="5" t="n">
         <v>46225</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="40" t="n">
         <f aca="false">F14-E14</f>
         <v>91</v>
       </c>
@@ -39176,14 +39499,14 @@
         <f aca="false">IF(ABS(L14)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O14" s="37"/>
+      <c r="O14" s="35"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="B15" s="37" t="s">
-        <v>1274</v>
+      <c r="B15" s="35" t="s">
+        <v>1300</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">Certificados!H15</f>
@@ -39198,7 +39521,7 @@
       <c r="F15" s="5" t="n">
         <v>46230</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="40" t="n">
         <f aca="false">F15-E15</f>
         <v>91</v>
       </c>
@@ -39229,14 +39552,14 @@
         <f aca="false">IF(ABS(L15)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O15" s="37"/>
+      <c r="O15" s="35"/>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="B16" s="37" t="s">
-        <v>1274</v>
+      <c r="B16" s="35" t="s">
+        <v>1300</v>
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">Certificados!H16</f>
@@ -39251,7 +39574,7 @@
       <c r="F16" s="5" t="n">
         <v>46230</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="40" t="n">
         <f aca="false">F16-E16</f>
         <v>91</v>
       </c>
@@ -39282,14 +39605,14 @@
         <f aca="false">IF(ABS(L16)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O16" s="37"/>
+      <c r="O16" s="35"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="B17" s="37" t="s">
-        <v>1275</v>
+      <c r="B17" s="35" t="s">
+        <v>1301</v>
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">Certificados!H17</f>
@@ -39304,7 +39627,7 @@
       <c r="F17" s="5" t="n">
         <v>46226</v>
       </c>
-      <c r="G17" s="39" t="n">
+      <c r="G17" s="40" t="n">
         <f aca="false">F17-E17</f>
         <v>91</v>
       </c>
@@ -39335,14 +39658,14 @@
         <f aca="false">IF(ABS(L17)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O17" s="37"/>
+      <c r="O17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="B18" s="37" t="s">
-        <v>1275</v>
+      <c r="B18" s="35" t="s">
+        <v>1301</v>
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">Certificados!H18</f>
@@ -39357,7 +39680,7 @@
       <c r="F18" s="5" t="n">
         <v>46226</v>
       </c>
-      <c r="G18" s="39" t="n">
+      <c r="G18" s="40" t="n">
         <f aca="false">F18-E18</f>
         <v>91</v>
       </c>
@@ -39388,14 +39711,14 @@
         <f aca="false">IF(ABS(L18)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O18" s="37"/>
+      <c r="O18" s="35"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="B19" s="37" t="s">
-        <v>1276</v>
+      <c r="B19" s="35" t="s">
+        <v>1302</v>
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">Certificados!H19</f>
@@ -39410,7 +39733,7 @@
       <c r="F19" s="5" t="n">
         <v>46223</v>
       </c>
-      <c r="G19" s="39" t="n">
+      <c r="G19" s="40" t="n">
         <f aca="false">F19-E19</f>
         <v>91</v>
       </c>
@@ -39441,11 +39764,11 @@
         <f aca="false">IF(ABS(L19)&lt;=Resumen!$C$7,"Razonable","Diferencia")</f>
         <v>Razonable</v>
       </c>
-      <c r="O19" s="37"/>
+      <c r="O19" s="35"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="J20" s="20" t="n">
         <f aca="false">SUM(J6:J19)</f>
@@ -39455,14 +39778,14 @@
         <f aca="false">SUM(K6:K19)</f>
         <v>-51792495.0698545</v>
       </c>
-      <c r="L20" s="40" t="n">
+      <c r="L20" s="41" t="n">
         <f aca="false">K20/J20</f>
         <v>-0.0321107242341442</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>1277</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39470,40 +39793,40 @@
         <v>1021</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1278</v>
+        <v>1304</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>1279</v>
+        <v>1305</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1251</v>
+        <v>1277</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>1280</v>
+        <v>1306</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>1099</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>1254</v>
+        <v>1280</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>1281</v>
+        <v>1307</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>1282</v>
+        <v>1308</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>1283</v>
+        <v>1309</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>1284</v>
+        <v>1310</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>1285</v>
+        <v>1311</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>1286</v>
+        <v>1312</v>
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="9" t="s">
@@ -39515,7 +39838,7 @@
         <v>707</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C24" s="11" t="n">
         <f aca="false">Certificados!J5</f>
@@ -39530,7 +39853,7 @@
       <c r="F24" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G24" s="39" t="n">
+      <c r="G24" s="40" t="n">
         <f aca="false">F24-E24</f>
         <v>132</v>
       </c>
@@ -39545,19 +39868,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A24,Mayor_Mov!$B$5:$B$445,L24,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M24)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A24,Mayor_Mov!$B$5:$B$445,L24,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M24)</f>
         <v>372400000</v>
       </c>
-      <c r="K24" s="41" t="n">
+      <c r="K24" s="42" t="n">
         <f aca="false">I24-J24</f>
         <v>29058173.0714088</v>
       </c>
       <c r="L24" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M24" s="42" t="n">
+      <c r="M24" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A24,Mayor_Mov!$B$5:$B$445,L24,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46105</v>
       </c>
-      <c r="O24" s="37" t="s">
-        <v>1288</v>
+      <c r="O24" s="35" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39565,13 +39888,13 @@
         <v>709</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>1289</v>
+        <v>1315</v>
       </c>
       <c r="C25" s="11" t="n">
         <f aca="false">Certificados!J11</f>
         <v>3959997817.95</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("DAV-607691",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.160198265625</v>
       </c>
@@ -39581,7 +39904,7 @@
       <c r="F25" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G25" s="39" t="n">
+      <c r="G25" s="40" t="n">
         <f aca="false">F25-E25</f>
         <v>3</v>
       </c>
@@ -39596,19 +39919,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A25,Mayor_Mov!$B$5:$B$445,L25,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M25)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A25,Mayor_Mov!$B$5:$B$445,L25,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M25)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="41" t="n">
+      <c r="K25" s="42" t="n">
         <f aca="false">I25-J25</f>
         <v>4839280.59774044</v>
       </c>
       <c r="L25" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M25" s="42" t="n">
+      <c r="M25" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A25,Mayor_Mov!$B$5:$B$445,L25,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O25" s="37" t="s">
-        <v>1290</v>
+      <c r="O25" s="35" t="s">
+        <v>1316</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39616,13 +39939,13 @@
         <v>712</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>1289</v>
+        <v>1315</v>
       </c>
       <c r="C26" s="11" t="n">
         <f aca="false">Certificados!J12</f>
         <v>2999995157</v>
       </c>
-      <c r="D26" s="35" t="n">
+      <c r="D26" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("DAV-569032",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.160198265625</v>
       </c>
@@ -39632,7 +39955,7 @@
       <c r="F26" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G26" s="39" t="n">
+      <c r="G26" s="40" t="n">
         <f aca="false">F26-E26</f>
         <v>3</v>
       </c>
@@ -39647,19 +39970,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A26,Mayor_Mov!$B$5:$B$445,L26,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M26)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A26,Mayor_Mov!$B$5:$B$445,L26,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M26)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="41" t="n">
+      <c r="K26" s="42" t="n">
         <f aca="false">I26-J26</f>
         <v>3666117.76672668</v>
       </c>
       <c r="L26" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M26" s="42" t="n">
+      <c r="M26" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A26,Mayor_Mov!$B$5:$B$445,L26,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O26" s="37" t="s">
-        <v>1291</v>
+      <c r="O26" s="35" t="s">
+        <v>1317</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39667,13 +39990,13 @@
         <v>91</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>1292</v>
+        <v>1318</v>
       </c>
       <c r="C27" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"BBVA-0141")</f>
         <v>4700000000</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("BBVA-0141",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.135423288111736</v>
       </c>
@@ -39683,7 +40006,7 @@
       <c r="F27" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G27" s="39" t="n">
+      <c r="G27" s="40" t="n">
         <f aca="false">F27-E27</f>
         <v>31</v>
       </c>
@@ -39698,19 +40021,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A27,Mayor_Mov!$B$5:$B$445,L27,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M27)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A27,Mayor_Mov!$B$5:$B$445,L27,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M27)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="41" t="n">
+      <c r="K27" s="42" t="n">
         <f aca="false">I27-J27</f>
         <v>50972239.5760856</v>
       </c>
       <c r="L27" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M27" s="42" t="n">
+      <c r="M27" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A27,Mayor_Mov!$B$5:$B$445,L27,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46203</v>
       </c>
-      <c r="O27" s="37" t="s">
-        <v>1293</v>
+      <c r="O27" s="35" t="s">
+        <v>1319</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39718,7 +40041,7 @@
         <v>112</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C28" s="11" t="n">
         <f aca="false">Certificados!J8</f>
@@ -39733,7 +40056,7 @@
       <c r="F28" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G28" s="39" t="n">
+      <c r="G28" s="40" t="n">
         <f aca="false">F28-E28</f>
         <v>14</v>
       </c>
@@ -39748,19 +40071,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A28,Mayor_Mov!$B$5:$B$445,L28,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M28)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A28,Mayor_Mov!$B$5:$B$445,L28,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M28)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="41" t="n">
+      <c r="K28" s="42" t="n">
         <f aca="false">I28-J28</f>
         <v>17704418.3193534</v>
       </c>
       <c r="L28" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M28" s="42" t="n">
+      <c r="M28" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A28,Mayor_Mov!$B$5:$B$445,L28,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>0</v>
       </c>
-      <c r="O28" s="37" t="s">
-        <v>1294</v>
+      <c r="O28" s="35" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39768,7 +40091,7 @@
         <v>121</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C29" s="11" t="n">
         <f aca="false">Certificados!J6</f>
@@ -39783,7 +40106,7 @@
       <c r="F29" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G29" s="39" t="n">
+      <c r="G29" s="40" t="n">
         <f aca="false">F29-E29</f>
         <v>40</v>
       </c>
@@ -39798,19 +40121,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A29,Mayor_Mov!$B$5:$B$445,L29,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M29)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A29,Mayor_Mov!$B$5:$B$445,L29,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M29)</f>
         <v>17825616</v>
       </c>
-      <c r="K29" s="41" t="n">
+      <c r="K29" s="42" t="n">
         <f aca="false">I29-J29</f>
         <v>4896273.98129553</v>
       </c>
       <c r="L29" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M29" s="42" t="n">
+      <c r="M29" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A29,Mayor_Mov!$B$5:$B$445,L29,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46203</v>
       </c>
-      <c r="O29" s="37" t="s">
-        <v>1295</v>
+      <c r="O29" s="35" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39818,7 +40141,7 @@
         <v>118</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C30" s="11" t="n">
         <f aca="false">Certificados!J9</f>
@@ -39833,7 +40156,7 @@
       <c r="F30" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G30" s="39" t="n">
+      <c r="G30" s="40" t="n">
         <f aca="false">F30-E30</f>
         <v>67</v>
       </c>
@@ -39848,19 +40171,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A30,Mayor_Mov!$B$5:$B$445,L30,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M30)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A30,Mayor_Mov!$B$5:$B$445,L30,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M30)</f>
         <v>30088126</v>
       </c>
-      <c r="K30" s="41" t="n">
+      <c r="K30" s="42" t="n">
         <f aca="false">I30-J30</f>
         <v>2623824.34698591</v>
       </c>
       <c r="L30" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M30" s="42" t="n">
+      <c r="M30" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A30,Mayor_Mov!$B$5:$B$445,L30,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46164</v>
       </c>
-      <c r="O30" s="37" t="s">
-        <v>1295</v>
+      <c r="O30" s="35" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39868,13 +40191,13 @@
         <v>102</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>1296</v>
+        <v>1322</v>
       </c>
       <c r="C31" s="11" t="n">
         <f aca="false">Certificados!J10</f>
         <v>10000000000</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("BOG-1159383796",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.1296288656</v>
       </c>
@@ -39884,7 +40207,7 @@
       <c r="F31" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G31" s="39" t="n">
+      <c r="G31" s="40" t="n">
         <f aca="false">F31-E31</f>
         <v>9</v>
       </c>
@@ -39899,19 +40222,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A31,Mayor_Mov!$B$5:$B$445,L31,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M31)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A31,Mayor_Mov!$B$5:$B$445,L31,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M31)</f>
         <v>0</v>
       </c>
-      <c r="K31" s="41" t="n">
+      <c r="K31" s="42" t="n">
         <f aca="false">I31-J31</f>
         <v>30518760.5171553</v>
       </c>
       <c r="L31" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M31" s="42" t="n">
+      <c r="M31" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A31,Mayor_Mov!$B$5:$B$445,L31,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46230</v>
       </c>
-      <c r="O31" s="37" t="s">
-        <v>1297</v>
+      <c r="O31" s="35" t="s">
+        <v>1323</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39919,13 +40242,13 @@
         <v>140</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>1292</v>
+        <v>1318</v>
       </c>
       <c r="C32" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"POP-631309940")</f>
         <v>287500000</v>
       </c>
-      <c r="D32" s="35" t="n">
+      <c r="D32" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("POP-631309940",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.149386780746296</v>
       </c>
@@ -39935,7 +40258,7 @@
       <c r="F32" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G32" s="39" t="n">
+      <c r="G32" s="40" t="n">
         <f aca="false">F32-E32</f>
         <v>44</v>
       </c>
@@ -39950,19 +40273,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A32,Mayor_Mov!$B$5:$B$445,L32,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M32)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A32,Mayor_Mov!$B$5:$B$445,L32,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M32)</f>
         <v>3324938</v>
       </c>
-      <c r="K32" s="41" t="n">
+      <c r="K32" s="42" t="n">
         <f aca="false">I32-J32</f>
         <v>1541101.68585017</v>
       </c>
       <c r="L32" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M32" s="42" t="n">
+      <c r="M32" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A32,Mayor_Mov!$B$5:$B$445,L32,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46203</v>
       </c>
-      <c r="O32" s="37" t="s">
-        <v>1298</v>
+      <c r="O32" s="35" t="s">
+        <v>1324</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39970,7 +40293,7 @@
         <v>147</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C33" s="11" t="n">
         <f aca="false">Certificados!J7</f>
@@ -39985,7 +40308,7 @@
       <c r="F33" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G33" s="39" t="n">
+      <c r="G33" s="40" t="n">
         <f aca="false">F33-E33</f>
         <v>9</v>
       </c>
@@ -40000,19 +40323,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A33,Mayor_Mov!$B$5:$B$445,L33,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M33)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A33,Mayor_Mov!$B$5:$B$445,L33,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M33)</f>
         <v>0</v>
       </c>
-      <c r="K33" s="41" t="n">
+      <c r="K33" s="42" t="n">
         <f aca="false">I33-J33</f>
         <v>10909736.1129754</v>
       </c>
       <c r="L33" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="M33" s="42" t="n">
+      <c r="M33" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A33,Mayor_Mov!$B$5:$B$445,L33,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O33" s="37" t="s">
-        <v>1299</v>
+      <c r="O33" s="35" t="s">
+        <v>1325</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40020,7 +40343,7 @@
         <v>805</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>1300</v>
+        <v>1326</v>
       </c>
       <c r="C34" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"DAV-L1021275")</f>
@@ -40035,7 +40358,7 @@
       <c r="F34" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G34" s="39" t="n">
+      <c r="G34" s="40" t="n">
         <f aca="false">F34-E34</f>
         <v>8</v>
       </c>
@@ -40050,25 +40373,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A34,Mayor_Mov!$B$5:$B$445,L34,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M34)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A34,Mayor_Mov!$B$5:$B$445,L34,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M34)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="41" t="n">
+      <c r="K34" s="42" t="n">
         <f aca="false">I34-J34</f>
         <v>5566172.27019184</v>
       </c>
       <c r="L34" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M34" s="42" t="n">
+      <c r="M34" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A34,Mayor_Mov!$B$5:$B$445,L34,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O34" s="37"/>
+      <c r="O34" s="35"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
         <v>576</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>1300</v>
+        <v>1326</v>
       </c>
       <c r="C35" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"DAV-L1019441")</f>
@@ -40083,7 +40406,7 @@
       <c r="F35" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G35" s="39" t="n">
+      <c r="G35" s="40" t="n">
         <f aca="false">F35-E35</f>
         <v>18</v>
       </c>
@@ -40098,25 +40421,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A35,Mayor_Mov!$B$5:$B$445,L35,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M35)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A35,Mayor_Mov!$B$5:$B$445,L35,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M35)</f>
         <v>0</v>
       </c>
-      <c r="K35" s="41" t="n">
+      <c r="K35" s="42" t="n">
         <f aca="false">I35-J35</f>
         <v>2933182.34708288</v>
       </c>
       <c r="L35" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M35" s="42" t="n">
+      <c r="M35" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A35,Mayor_Mov!$B$5:$B$445,L35,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>0</v>
       </c>
-      <c r="O35" s="37"/>
+      <c r="O35" s="35"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
         <v>572</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>1300</v>
+        <v>1326</v>
       </c>
       <c r="C36" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"DAV-L1019448")</f>
@@ -40131,7 +40454,7 @@
       <c r="F36" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G36" s="39" t="n">
+      <c r="G36" s="40" t="n">
         <f aca="false">F36-E36</f>
         <v>25</v>
       </c>
@@ -40146,25 +40469,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A36,Mayor_Mov!$B$5:$B$445,L36,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M36)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A36,Mayor_Mov!$B$5:$B$445,L36,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M36)</f>
         <v>0</v>
       </c>
-      <c r="K36" s="41" t="n">
+      <c r="K36" s="42" t="n">
         <f aca="false">I36-J36</f>
         <v>3292184.55349193</v>
       </c>
       <c r="L36" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M36" s="42" t="n">
+      <c r="M36" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A36,Mayor_Mov!$B$5:$B$445,L36,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>0</v>
       </c>
-      <c r="O36" s="37"/>
+      <c r="O36" s="35"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
         <v>615</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C37" s="11" t="n">
         <f aca="false">Certificados!J14</f>
@@ -40179,7 +40502,7 @@
       <c r="F37" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G37" s="39" t="n">
+      <c r="G37" s="40" t="n">
         <f aca="false">F37-E37</f>
         <v>9</v>
       </c>
@@ -40194,25 +40517,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A37,Mayor_Mov!$B$5:$B$445,L37,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M37)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A37,Mayor_Mov!$B$5:$B$445,L37,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M37)</f>
         <v>0</v>
       </c>
-      <c r="K37" s="41" t="n">
+      <c r="K37" s="42" t="n">
         <f aca="false">I37-J37</f>
         <v>3617017.21971566</v>
       </c>
       <c r="L37" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M37" s="42" t="n">
+      <c r="M37" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A37,Mayor_Mov!$B$5:$B$445,L37,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O37" s="37"/>
+      <c r="O37" s="35"/>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
         <v>609</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C38" s="11" t="n">
         <f aca="false">Certificados!J15</f>
@@ -40227,7 +40550,7 @@
       <c r="F38" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G38" s="39" t="n">
+      <c r="G38" s="40" t="n">
         <f aca="false">F38-E38</f>
         <v>4</v>
       </c>
@@ -40242,25 +40565,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A38,Mayor_Mov!$B$5:$B$445,L38,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M38)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A38,Mayor_Mov!$B$5:$B$445,L38,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M38)</f>
         <v>0</v>
       </c>
-      <c r="K38" s="41" t="n">
+      <c r="K38" s="42" t="n">
         <f aca="false">I38-J38</f>
         <v>370614.629483698</v>
       </c>
       <c r="L38" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M38" s="42" t="n">
+      <c r="M38" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A38,Mayor_Mov!$B$5:$B$445,L38,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46230</v>
       </c>
-      <c r="O38" s="37"/>
+      <c r="O38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
         <v>606</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C39" s="11" t="n">
         <f aca="false">Certificados!J16</f>
@@ -40275,7 +40598,7 @@
       <c r="F39" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G39" s="39" t="n">
+      <c r="G39" s="40" t="n">
         <f aca="false">F39-E39</f>
         <v>4</v>
       </c>
@@ -40290,25 +40613,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A39,Mayor_Mov!$B$5:$B$445,L39,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M39)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A39,Mayor_Mov!$B$5:$B$445,L39,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M39)</f>
         <v>0</v>
       </c>
-      <c r="K39" s="41" t="n">
+      <c r="K39" s="42" t="n">
         <f aca="false">I39-J39</f>
         <v>370614.629600578</v>
       </c>
       <c r="L39" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M39" s="42" t="n">
+      <c r="M39" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A39,Mayor_Mov!$B$5:$B$445,L39,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46230</v>
       </c>
-      <c r="O39" s="37"/>
+      <c r="O39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
         <v>618</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C40" s="11" t="n">
         <f aca="false">Certificados!J17</f>
@@ -40323,7 +40646,7 @@
       <c r="F40" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G40" s="39" t="n">
+      <c r="G40" s="40" t="n">
         <f aca="false">F40-E40</f>
         <v>8</v>
       </c>
@@ -40338,25 +40661,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A40,Mayor_Mov!$B$5:$B$445,L40,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M40)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A40,Mayor_Mov!$B$5:$B$445,L40,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M40)</f>
         <v>0</v>
       </c>
-      <c r="K40" s="41" t="n">
+      <c r="K40" s="42" t="n">
         <f aca="false">I40-J40</f>
         <v>1155997.19975989</v>
       </c>
       <c r="L40" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M40" s="42" t="n">
+      <c r="M40" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A40,Mayor_Mov!$B$5:$B$445,L40,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O40" s="37"/>
+      <c r="O40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
         <v>621</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C41" s="11" t="n">
         <f aca="false">Certificados!J18</f>
@@ -40371,7 +40694,7 @@
       <c r="F41" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G41" s="39" t="n">
+      <c r="G41" s="40" t="n">
         <f aca="false">F41-E41</f>
         <v>8</v>
       </c>
@@ -40386,25 +40709,25 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A41,Mayor_Mov!$B$5:$B$445,L41,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M41)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A41,Mayor_Mov!$B$5:$B$445,L41,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="41" t="n">
+      <c r="K41" s="42" t="n">
         <f aca="false">I41-J41</f>
         <v>1155997.19932213</v>
       </c>
       <c r="L41" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M41" s="42" t="n">
+      <c r="M41" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A41,Mayor_Mov!$B$5:$B$445,L41,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O41" s="37"/>
+      <c r="O41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
         <v>612</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="C42" s="11" t="n">
         <f aca="false">Certificados!J19</f>
@@ -40419,7 +40742,7 @@
       <c r="F42" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G42" s="39" t="n">
+      <c r="G42" s="40" t="n">
         <f aca="false">F42-E42</f>
         <v>11</v>
       </c>
@@ -40434,31 +40757,31 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A42,Mayor_Mov!$B$5:$B$445,L42,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M42)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A42,Mayor_Mov!$B$5:$B$445,L42,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M42)</f>
         <v>0</v>
       </c>
-      <c r="K42" s="41" t="n">
+      <c r="K42" s="42" t="n">
         <f aca="false">I42-J42</f>
         <v>1590694.25438737</v>
       </c>
       <c r="L42" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M42" s="42" t="n">
+      <c r="M42" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A42,Mayor_Mov!$B$5:$B$445,L42,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46231</v>
       </c>
-      <c r="O42" s="37"/>
+      <c r="O42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
         <v>662</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>1292</v>
+        <v>1318</v>
       </c>
       <c r="C43" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"BCL-L362095")</f>
         <v>497241599</v>
       </c>
-      <c r="D43" s="35" t="n">
+      <c r="D43" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("BCL-L362095",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.156382742125655</v>
       </c>
@@ -40468,7 +40791,7 @@
       <c r="F43" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G43" s="39" t="n">
+      <c r="G43" s="40" t="n">
         <f aca="false">F43-E43</f>
         <v>31</v>
       </c>
@@ -40483,19 +40806,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A43,Mayor_Mov!$B$5:$B$445,L43,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M43)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A43,Mayor_Mov!$B$5:$B$445,L43,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M43)</f>
         <v>3750337</v>
       </c>
-      <c r="K43" s="41" t="n">
+      <c r="K43" s="42" t="n">
         <f aca="false">I43-J43</f>
         <v>2423778.75656886</v>
       </c>
       <c r="L43" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M43" s="42" t="n">
+      <c r="M43" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A43,Mayor_Mov!$B$5:$B$445,L43,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>46203</v>
       </c>
-      <c r="O43" s="37" t="s">
-        <v>1301</v>
+      <c r="O43" s="35" t="s">
+        <v>1327</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40503,13 +40826,13 @@
         <v>651</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>1292</v>
+        <v>1318</v>
       </c>
       <c r="C44" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"BCL-L336817")</f>
         <v>770085425.158301</v>
       </c>
-      <c r="D44" s="35" t="n">
+      <c r="D44" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("BCL-L336817",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.157948891345503</v>
       </c>
@@ -40519,7 +40842,7 @@
       <c r="F44" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G44" s="39" t="n">
+      <c r="G44" s="40" t="n">
         <f aca="false">F44-E44</f>
         <v>12</v>
       </c>
@@ -40534,19 +40857,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A44,Mayor_Mov!$B$5:$B$445,L44,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M44)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A44,Mayor_Mov!$B$5:$B$445,L44,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M44)</f>
         <v>0</v>
       </c>
-      <c r="K44" s="41" t="n">
+      <c r="K44" s="42" t="n">
         <f aca="false">I44-J44</f>
         <v>3721837.79385868</v>
       </c>
       <c r="L44" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M44" s="42" t="n">
+      <c r="M44" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A44,Mayor_Mov!$B$5:$B$445,L44,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>0</v>
       </c>
-      <c r="O44" s="37" t="s">
-        <v>1302</v>
+      <c r="O44" s="35" t="s">
+        <v>1328</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40554,13 +40877,13 @@
         <v>648</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>1292</v>
+        <v>1318</v>
       </c>
       <c r="C45" s="11" t="n">
         <f aca="false">SUMIFS(Detalle_62!$F$14:$F$35,Detalle_62!$C$14:$C$35,"BCL-L331330")</f>
         <v>503693510</v>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="36" t="n">
         <f aca="false">INDEX(Detalle_62!$J$14:$J$35,MATCH("BCL-L331330",Detalle_62!$C$14:$C$35,0))</f>
         <v>0.164255943222499</v>
       </c>
@@ -40570,7 +40893,7 @@
       <c r="F45" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G45" s="39" t="n">
+      <c r="G45" s="40" t="n">
         <f aca="false">F45-E45</f>
         <v>22</v>
       </c>
@@ -40585,19 +40908,19 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A45,Mayor_Mov!$B$5:$B$445,L45,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M45)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A45,Mayor_Mov!$B$5:$B$445,L45,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M45)</f>
         <v>0</v>
       </c>
-      <c r="K45" s="41" t="n">
+      <c r="K45" s="42" t="n">
         <f aca="false">I45-J45</f>
         <v>4638382.95143143</v>
       </c>
       <c r="L45" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M45" s="42" t="n">
+      <c r="M45" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A45,Mayor_Mov!$B$5:$B$445,L45,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>0</v>
       </c>
-      <c r="O45" s="37" t="s">
-        <v>1303</v>
+      <c r="O45" s="35" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40605,13 +40928,13 @@
         <v>552</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>1304</v>
+        <v>1330</v>
       </c>
       <c r="C46" s="11" t="n">
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,"BCL-L386735")</f>
         <v>675837500</v>
       </c>
-      <c r="D46" s="35" t="n">
+      <c r="D46" s="36" t="n">
         <f aca="false">(1+(Detalle_62!$B$6+0.0135)/4)^4-1</f>
         <v>0.137775314543555</v>
       </c>
@@ -40621,7 +40944,7 @@
       <c r="F46" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="G46" s="39" t="n">
+      <c r="G46" s="40" t="n">
         <f aca="false">F46-E46</f>
         <v>3</v>
       </c>
@@ -40636,24 +40959,24 @@
         <f aca="false">SUMIFS(Mayor_Mov!$F$5:$F$445,Mayor_Mov!$N$5:$N$445,A46,Mayor_Mov!$B$5:$B$445,L46,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M46)-SUMIFS(Mayor_Mov!$E$5:$E$445,Mayor_Mov!$N$5:$N$445,A46,Mayor_Mov!$B$5:$B$445,L46,Mayor_Mov!$H$5:$H$445,"&gt;"&amp;M46)</f>
         <v>0</v>
       </c>
-      <c r="K46" s="41" t="n">
+      <c r="K46" s="42" t="n">
         <f aca="false">I46-J46</f>
         <v>717369.299115863</v>
       </c>
       <c r="L46" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="M46" s="42" t="n">
+      <c r="M46" s="43" t="n">
         <f aca="false">_xlfn.MAXIFS(Mayor_Mov!$H$5:$H$445,Mayor_Mov!$N$5:$N$445,A46,Mayor_Mov!$B$5:$B$445,L46,Mayor_Mov!$E$5:$E$445,"&gt;1000")</f>
         <v>0</v>
       </c>
-      <c r="O46" s="37" t="s">
-        <v>1305</v>
+      <c r="O46" s="35" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="19" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="I47" s="20" t="n">
         <f aca="false">SUM(I24:I46)</f>
@@ -40670,7 +40993,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>1306</v>
+        <v>1332</v>
       </c>
       <c r="I48" s="12" t="n">
         <f aca="false">SUMIFS(I24:I46,$L$24:$L$46,"21300101")</f>
@@ -40687,7 +41010,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="s">
-        <v>1307</v>
+        <v>1333</v>
       </c>
       <c r="I49" s="12" t="n">
         <f aca="false">SUMIFS(I24:I46,$L$24:$L$46,"21300102")</f>
@@ -40704,7 +41027,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>1308</v>
+        <v>1334</v>
       </c>
       <c r="J50" s="11" t="n">
         <f aca="false">-Balance_21!$F$25</f>
@@ -40713,19 +41036,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>1309</v>
+        <v>1335</v>
       </c>
       <c r="J51" s="12" t="n">
         <f aca="false">J47-J50</f>
         <v>-0.160000026226044</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>1310</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>1311</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40733,37 +41056,37 @@
         <v>1021</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1312</v>
+        <v>1338</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1313</v>
+        <v>1339</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>1251</v>
+        <v>1277</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>1252</v>
+        <v>1278</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>1253</v>
+        <v>1279</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>1254</v>
+        <v>1280</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>1314</v>
+        <v>1340</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>1315</v>
+        <v>1341</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>1316</v>
+        <v>1342</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>1103</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>1317</v>
+        <v>1343</v>
       </c>
       <c r="M54" s="9"/>
       <c r="N54" s="9"/>
@@ -40776,7 +41099,7 @@
         <v>805</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>1318</v>
+        <v>1344</v>
       </c>
       <c r="C55" s="18" t="n">
         <v>64041851</v>
@@ -40790,7 +41113,7 @@
       <c r="F55" s="5" t="n">
         <v>46226</v>
       </c>
-      <c r="G55" s="39" t="n">
+      <c r="G55" s="40" t="n">
         <f aca="false">F55-E55</f>
         <v>91</v>
       </c>
@@ -40813,8 +41136,8 @@
         <f aca="false">K55-J55</f>
         <v>7409615.50000811</v>
       </c>
-      <c r="O55" s="37" t="s">
-        <v>1319</v>
+      <c r="O55" s="35" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40822,7 +41145,7 @@
         <v>576</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>1320</v>
+        <v>1346</v>
       </c>
       <c r="C56" s="18" t="n">
         <v>5062372</v>
@@ -40836,7 +41159,7 @@
       <c r="F56" s="5" t="n">
         <v>46216</v>
       </c>
-      <c r="G56" s="39" t="n">
+      <c r="G56" s="40" t="n">
         <f aca="false">F56-E56</f>
         <v>32</v>
       </c>
@@ -40859,8 +41182,8 @@
         <f aca="false">K56-J56</f>
         <v>25062625.3318693</v>
       </c>
-      <c r="O56" s="37" t="s">
-        <v>1319</v>
+      <c r="O56" s="35" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40868,7 +41191,7 @@
         <v>572</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="C57" s="18" t="n">
         <v>4177893</v>
@@ -40882,7 +41205,7 @@
       <c r="F57" s="5" t="n">
         <v>46209</v>
       </c>
-      <c r="G57" s="39" t="n">
+      <c r="G57" s="40" t="n">
         <f aca="false">F57-E57</f>
         <v>31</v>
       </c>
@@ -40905,13 +41228,13 @@
         <f aca="false">K57-J57</f>
         <v>1694924.67585093</v>
       </c>
-      <c r="O57" s="37" t="s">
-        <v>1319</v>
+      <c r="O57" s="35" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="19" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="J58" s="20" t="n">
         <f aca="false">SUM(J55:J57)</f>
@@ -40953,12 +41276,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1322</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1323</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40966,179 +41289,179 @@
         <v>987</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>1217</v>
+        <v>1243</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>1324</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1325</v>
+        <v>1351</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">-(Balance_21!$C$16+Balance_21!$C$18+Balance_21!$C$20)</f>
         <v>49437161409.34</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>1326</v>
+      <c r="C4" s="44" t="s">
+        <v>1352</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1327</v>
+        <v>1353</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">-(Balance_21!$F$16+Balance_21!$F$18+Balance_21!$F$20)</f>
         <v>46204178294.33</v>
       </c>
-      <c r="C5" s="43" t="s">
-        <v>1326</v>
+      <c r="C5" s="44" t="s">
+        <v>1352</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1328</v>
+        <v>1354</v>
       </c>
       <c r="B6" s="12" t="n">
         <f aca="false">AVERAGE(B4:B5)</f>
         <v>47820669851.835</v>
       </c>
-      <c r="C6" s="43"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1329</v>
-      </c>
-      <c r="B7" s="35" t="n">
+        <v>1355</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <f aca="false">Detalle_62!$F$48</f>
         <v>0.149092952439153</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>1330</v>
+      <c r="C7" s="44" t="s">
+        <v>1356</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B8" s="39" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B8" s="40" t="n">
         <f aca="false">DATE(2026,7,31)-DATE(2025,12,31)</f>
         <v>212</v>
       </c>
-      <c r="C8" s="43"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>1332</v>
+        <v>1358</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">B6*((1+B7)^(B8/365)-1)</f>
         <v>4020077715.73674</v>
       </c>
-      <c r="C9" s="43"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>1333</v>
+        <v>1359</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">Balance_21!$F$33</f>
         <v>615032539.99</v>
       </c>
-      <c r="C10" s="43"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>1334</v>
+        <v>1360</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">Balance_21!$F$34</f>
         <v>2503471375.89</v>
       </c>
-      <c r="C11" s="43"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>1335</v>
+        <v>1361</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">Balance_21!$F$35</f>
         <v>423638680</v>
       </c>
-      <c r="C12" s="43"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>1336</v>
+        <v>1362</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">Balance_21!$F$36</f>
         <v>3750337.32</v>
       </c>
-      <c r="C13" s="43"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>1337</v>
+        <v>1363</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">SUM(B10:B13)</f>
         <v>3545892933.2</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>1338</v>
+      <c r="C14" s="44" t="s">
+        <v>1364</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>1339</v>
+        <v>1365</v>
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">Recalculo_Intereses!K47</f>
         <v>188283769.079588</v>
       </c>
-      <c r="C15" s="43"/>
+      <c r="C15" s="44"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>1340</v>
+        <v>1366</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">B14+B15</f>
         <v>3734176702.27959</v>
       </c>
-      <c r="C16" s="43"/>
+      <c r="C16" s="44"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>1341</v>
+        <v>1367</v>
       </c>
       <c r="B17" s="12" t="n">
         <f aca="false">B16-B9</f>
         <v>-285901013.457154</v>
       </c>
-      <c r="C17" s="43"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>1342</v>
+        <v>1368</v>
       </c>
       <c r="B18" s="33" t="n">
         <f aca="false">B17/B9</f>
         <v>-0.0711182802108487</v>
       </c>
-      <c r="C18" s="43"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>1343</v>
+        <v>1369</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>1344</v>
+      <c r="C19" s="44" t="s">
+        <v>1370</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41149,18 +41472,18 @@
         <f aca="false">IF(ABS(B18)&lt;=B19,"Gasto razonable dentro del umbral","Fuera de umbral – investigar")</f>
         <v>Gasto razonable dentro del umbral</v>
       </c>
-      <c r="C20" s="43"/>
+      <c r="C20" s="44"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>1345</v>
+        <v>1371</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">Balance_21!$F$32</f>
         <v>14723000.39</v>
       </c>
-      <c r="C21" s="43" t="s">
-        <v>1346</v>
+      <c r="C21" s="44" t="s">
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
